--- a/DOSSIES_MULTIFORMATO/PGE/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/PGE/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE00372</t>
+          <t>2020NE00121</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1012.66</v>
+        <v>10302.59</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE00363</t>
+          <t>2020NE00118</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>240.81</v>
+        <v>300.49</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2020NE00118</t>
+          <t>2020NE00363</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>300.49</v>
+        <v>240.81</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2020NE00121</t>
+          <t>2020NE00372</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10302.59</v>
+        <v>1012.66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -766,17 +766,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2016NE00402</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>2016NE00406</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2/2019</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>30/12/2016</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1275.58</v>
+        <v>4892.18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -785,14 +789,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0252,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
+          <t>Anulação total do saldo da NE 0271,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2016NE00405</t>
+          <t>2016NE00399</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -802,7 +806,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1676.89</v>
+        <v>6142.66</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -811,7 +815,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0314,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
+          <t>Anulação total do saldo da NE 0031,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
         </is>
       </c>
     </row>
@@ -844,7 +848,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2016NE00399</t>
+          <t>2016NE00405</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -854,7 +858,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6142.66</v>
+        <v>1676.89</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -863,28 +867,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0031,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
+          <t>Anulação total do saldo da NE 0314,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2016NE00406</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2/2019</t>
-        </is>
-      </c>
+          <t>2016NE00402</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>30/12/2016</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4892.18</v>
+        <v>1275.58</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -893,28 +893,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anulação total do saldo da NE 0271,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
+          <t>Anulação total do saldo da NE 0252,para atender à Instrução Normativa nº.01/2016-SET/SEFAZ, que dispõe sobre os procedimentos para o encerramento de 2016.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025NE0000430</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>13/2024</t>
-        </is>
-      </c>
+          <t>2025NE0000431</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>30/10/2025</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7607.43</v>
+        <v>403078.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -923,24 +919,28 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025NE0000431</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>2025NE0000430</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13/2024</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>30/10/2025</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>403078.1</v>
+        <v>7607.43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2022NE0000505</t>
+          <t>2022NE0000501</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>614.78</v>
+        <v>719.85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anulação do saldo da da NE nº.0365, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contábil do e</t>
+          <t>Anulação do saldo da da NE nº.0239, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contábil do e</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2022NE0000501</t>
+          <t>2022NE0000505</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>719.85</v>
+        <v>614.78</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1083,14 +1083,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anulação do saldo da da NE nº.0239, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contábil do e</t>
+          <t>Anulação do saldo da da NE nº.0365, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contábil do e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2017NE00400</t>
+          <t>2017NE00382</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>136</v>
+        <v>12540.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1109,14 +1109,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício.</t>
+          <t>Anulação de saldo por encerramento do exercício e término do 1º.Termo Aditivo ao Contrato nº.006/2015-PGE,celebrado entre a PGE e a Prodam Processamento de Dados. Objeto:Contratação para os serviços d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2017NE00398</t>
+          <t>2017NE00383</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1254.12</v>
+        <v>0.29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1135,14 +1135,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício.</t>
+          <t>Anulação de saldo por encerramento do exercício e término do 2º.Termo Aditivo ao Contrato nº.02/2015-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas. Objeto:Contratação para a Hos</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2017NE00407</t>
+          <t>2017NE00381</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2389.25</v>
+        <v>68861.02</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1161,14 +1161,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício.</t>
+          <t>Anulação de saldo por encerramento do exercício. Termo de Contrato nº.09/2016-PGE, celebrado entre a PGE e Prodam Processamento de Dados Amazonas. Objeto:Contratação para a prestação dos serviços de E</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2017NE00401</t>
+          <t>2017NE00389</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1743.71</v>
+        <v>2.42</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício.</t>
+          <t>Anulação de saldo por encerramento do exercício e término da vigência do 3º. Termo Aditivo ao Contrato nº.02/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2017NE00399</t>
+          <t>2017NE00384</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>456.44</v>
+        <v>11690.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício.</t>
+          <t>Anulação de saldo por encerramento do exercício e término do 3º. Termo Aditivo ao Contrato nº.012/2014-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, prestação de serviços d</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2017NE00384</t>
+          <t>2017NE00399</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11690.2</v>
+        <v>456.44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1265,14 +1265,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício e término do 3º. Termo Aditivo ao Contrato nº.012/2014-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, prestação de serviços d</t>
+          <t>Anulação de saldo por encerramento do exercício.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2017NE00389</t>
+          <t>2017NE00401</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.42</v>
+        <v>1743.71</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício e término da vigência do 3º. Termo Aditivo ao Contrato nº.02/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Anulação de saldo por encerramento do exercício.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2017NE00381</t>
+          <t>2017NE00407</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68861.02</v>
+        <v>2389.25</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1317,14 +1317,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício. Termo de Contrato nº.09/2016-PGE, celebrado entre a PGE e Prodam Processamento de Dados Amazonas. Objeto:Contratação para a prestação dos serviços de E</t>
+          <t>Anulação de saldo por encerramento do exercício.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2017NE00383</t>
+          <t>2017NE00398</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.29</v>
+        <v>1254.12</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício e término do 2º.Termo Aditivo ao Contrato nº.02/2015-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas. Objeto:Contratação para a Hos</t>
+          <t>Anulação de saldo por encerramento do exercício.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2017NE00382</t>
+          <t>2017NE00400</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12540.9</v>
+        <v>136</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1369,14 +1369,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Anulação de saldo por encerramento do exercício e término do 1º.Termo Aditivo ao Contrato nº.006/2015-PGE,celebrado entre a PGE e a Prodam Processamento de Dados. Objeto:Contratação para os serviços d</t>
+          <t>Anulação de saldo por encerramento do exercício.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2019NE00357</t>
+          <t>2019NE00358</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>261.08</v>
+        <v>0.63</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1395,14 +1395,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.0229, relativo ao 1º. Termo Aditivo ao Contrato nº.007/2018-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a realização de</t>
+          <t>Referente a Anulação do saldo da NE Nº.0047 a liquidar, relativo ao 5º.Termo Aditivo ao Contrato nº.002/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2019NE00358</t>
+          <t>2019NE00357</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.63</v>
+        <v>261.08</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Referente a Anulação do saldo da NE Nº.0047 a liquidar, relativo ao 5º.Termo Aditivo ao Contrato nº.002/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente a Anulação Total do saldo da NE nº.0229, relativo ao 1º. Termo Aditivo ao Contrato nº.007/2018-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a realização de</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2023NE0000498</t>
+          <t>2023NE0000515</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>442.32</v>
+        <v>72291.45</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1507,14 +1507,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE nº.0004, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
+          <t>Anulação do saldo da NE nº.0314, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2023NE0000502</t>
+          <t>2023NE0000501</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5795.88</v>
+        <v>8704.58</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1533,14 +1533,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE nº.0009, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
+          <t>Anulação do saldo da NE nº.0008, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2023NE0000501</t>
+          <t>2023NE0000502</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8704.58</v>
+        <v>5795.88</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1559,14 +1559,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE nº.0008, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
+          <t>Anulação do saldo da NE nº.0009, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2023NE0000515</t>
+          <t>2023NE0000498</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>72291.45</v>
+        <v>442.32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1585,14 +1585,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE nº.0314, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
+          <t>Anulação do saldo da NE nº.0004, conforme Decreto nº.48.346 de 26.10.2023, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária, financeira e contábil do exe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2022NE0000488</t>
+          <t>2022NE0000487</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6742.75</v>
+        <v>1713.87</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anulação do saldo da da NE nº.028, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contábil do ex</t>
+          <t>Anulação parcial do saldo da da NE nº.0411, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contá</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2022NE0000487</t>
+          <t>2022NE0000488</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1713.87</v>
+        <v>6742.75</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1663,14 +1663,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anulação parcial do saldo da da NE nº.0411, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contá</t>
+          <t>Anulação do saldo da da NE nº.028, conforme Decreto nº.46.621 de 11.11.2022, que dispõe sobre os procedimentos a serem adotados para o encerramento da execução orçamentária,financeira e contábil do ex</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2018NE00455</t>
+          <t>2018NE00451</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>798.08</v>
+        <v>0.78</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1689,14 +1689,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anulação parcial do saldo da NE Nº.0307,para cumprir orientações contidas na Instrução Normativa nº.01/2018/SET/SEFAZ, de 30.11.2018, que dispõe sobre os procedimentos para o encerramento do exercício</t>
+          <t>Anulação do saldo da NE Nº.0183, para cumprir orientações contidas na Instrução Normativa nº.01/2018/SET/SEFAZ, de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício de 2018</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2018NE00452</t>
+          <t>2018NE00464</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.68</v>
+        <v>439.85</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1715,14 +1715,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE Nº.0188, para cumprir orientações contidas na Instrução Normativa nº.01/2018/SET/SEFAZ,de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício de 2018.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2018NE00478</t>
+          <t>2018NE00463</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>249.4</v>
+        <v>2688.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1741,14 +1741,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2018NE00473</t>
+          <t>2018NE00459</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>345.78</v>
+        <v>4.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1767,14 +1767,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t>Anulação do saldo da NE Nº.0416, para cumprir orientações contidas na Instrução Normativa nº.01/2018-SET/SEFAZ,de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício de 2018.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2018NE00472</t>
+          <t>2018NE00458</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2904.02</v>
+        <v>9893.68</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
+          <t xml:space="preserve">Anulação parcial do saldo da NE Nº.0288, para cumprir orientações contidas na Instrução Normativa nº.01/2018-SET/SEFAZ,de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício </t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2018NE00458</t>
+          <t>2018NE00472</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9893.68</v>
+        <v>2904.02</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1845,14 +1845,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anulação parcial do saldo da NE Nº.0288, para cumprir orientações contidas na Instrução Normativa nº.01/2018-SET/SEFAZ,de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício </t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2018NE00459</t>
+          <t>2018NE00473</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.8</v>
+        <v>345.78</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1871,14 +1871,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE Nº.0416, para cumprir orientações contidas na Instrução Normativa nº.01/2018-SET/SEFAZ,de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício de 2018.</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2018NE00463</t>
+          <t>2018NE00478</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2688.5</v>
+        <v>249.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1897,14 +1897,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
+          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI FEDERAL Nº 101/2000 (LEI DE RESPONSABILIDADE FISCAL.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2018NE00464</t>
+          <t>2018NE00452</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>439.85</v>
+        <v>1.68</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1923,14 +1923,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CANCELAMENTO DE SALDO DE EMPENHO A LIQUIDAR PARA AJUSTE ORÇAMENTÁRIO DE ENCERRAMENTO DO EXERCÍCIO DE 2018, EM CUMPRIMENTO AO ART. 42 DA LEI COMPLEMENTAR FEDERAL 101/2000 ( LEI DE RESPONSABILIDADE FISC</t>
+          <t>Anulação do saldo da NE Nº.0188, para cumprir orientações contidas na Instrução Normativa nº.01/2018/SET/SEFAZ,de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício de 2018.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2018NE00451</t>
+          <t>2018NE00455</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.78</v>
+        <v>798.08</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anulação do saldo da NE Nº.0183, para cumprir orientações contidas na Instrução Normativa nº.01/2018/SET/SEFAZ, de 30.11.2018,que dispõe sobre os procedimentos para o encerramento do exercício de 2018</t>
+          <t>Anulação parcial do saldo da NE Nº.0307,para cumprir orientações contidas na Instrução Normativa nº.01/2018/SET/SEFAZ, de 30.11.2018, que dispõe sobre os procedimentos para o encerramento do exercício</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2023NE0000314</t>
+          <t>2023NE0000313</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>156837.26</v>
+        <v>313674.52</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2005,14 +2005,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Referente a Anulação da NE Nº.0260/2023-PGE, para acerto no número do Processo.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2023NE0000313</t>
+          <t>2023NE0000314</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>313674.52</v>
+        <v>156837.26</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2031,19 +2031,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Referente a Anulação da NE Nº.0260/2023-PGE, para acerto no número do Processo.</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2022NE0000140</t>
+          <t>2022NE0000139</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>110133.3</v>
+        <v>23166.32</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE N° 020 relativo ao 2º.Termo Aditivo ao Contrato nº 006/2019-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a prestação de Serviços de Inform</t>
+          <t>Referente ao Reforço da NE Nº.0028.</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2022NE0000139</t>
+          <t>2022NE0000140</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2108,7 +2108,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>23166.32</v>
+        <v>110133.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2117,14 +2117,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.0028.</t>
+          <t>Referente ao Reforço da NE N° 020 relativo ao 2º.Termo Aditivo ao Contrato nº 006/2019-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a prestação de Serviços de Inform</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024NE0000591</t>
+          <t>2024NE0000590</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>32918.21</v>
+        <v>4760.74</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2143,14 +2143,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DE SALDO DE EMPENHO, CONFORME ART. 2º, I, DO DECRETO Nº 50.522 DE 22.10.2024 QUE DISPÕE SOBRE AS PROVIDÊNCIAS DO EXERCÍCIO DE 2024.</t>
+          <t>ANULAÇÃO PARCIAL DE SALDO DE EMPENHO, CONFORME ART. 2º, I, DO DECRETO Nº 50.522 DE 22.10.2024 QUE DISPÕE SOBRE AS PROVIDÊNCIAS DO EXERCÍCIO DE 2024.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2024NE0000579</t>
+          <t>2024NE0000580</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>42049.19</v>
+        <v>10000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024NE0000589</t>
+          <t>2024NE0000573</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2764.74</v>
+        <v>1070.78</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024NE0000573</t>
+          <t>2024NE0000589</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1070.78</v>
+        <v>2764.74</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024NE0000580</t>
+          <t>2024NE0000579</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10000</v>
+        <v>42049.19</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024NE0000590</t>
+          <t>2024NE0000591</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4760.74</v>
+        <v>32918.21</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DE SALDO DE EMPENHO, CONFORME ART. 2º, I, DO DECRETO Nº 50.522 DE 22.10.2024 QUE DISPÕE SOBRE AS PROVIDÊNCIAS DO EXERCÍCIO DE 2024.</t>
+          <t>ANULAÇÃO DE SALDO DE EMPENHO, CONFORME ART. 2º, I, DO DECRETO Nº 50.522 DE 22.10.2024 QUE DISPÕE SOBRE AS PROVIDÊNCIAS DO EXERCÍCIO DE 2024.</t>
         </is>
       </c>
     </row>
@@ -2310,12 +2310,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024NE0000360</t>
+          <t>2024NE0000359</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>503.24</v>
+        <v>12295.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2333,19 +2333,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024NE0000359</t>
+          <t>2024NE0000360</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12295.5</v>
+        <v>503.24</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2363,14 +2363,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024NE0000554</t>
+          <t>2024NE0000555</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8595.469999999999</v>
+        <v>3.43</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024NE0000555</t>
+          <t>2024NE0000554</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3.43</v>
+        <v>8595.469999999999</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2019NE00395</t>
+          <t>2019NE00516</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1043.55</v>
+        <v>11868.84</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Referente a Anulação Parcial do saldo da NE Nº.00304,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelo</t>
+          <t>Referente a Anulação Parcial do saldo da NE Nº.0149,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2019NE00384</t>
+          <t>2019NE00379</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>161.05</v>
+        <v>11.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2493,14 +2493,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE Nº.0228,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
+          <t>Referente a Anulação Total do saldo da NE Nº.0014,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2019NE00381</t>
+          <t>2019NE00380</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>9150.91</v>
+        <v>0.24</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2519,14 +2519,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE Nº.0018,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
+          <t>Referente a Anulação Total do saldo da NE Nº.0017,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2019NE00380</t>
+          <t>2019NE00381</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.24</v>
+        <v>9150.91</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2545,14 +2545,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE Nº.0017,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
+          <t>Referente a Anulação Total do saldo da NE Nº.0018,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2019NE00379</t>
+          <t>2019NE00384</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.6</v>
+        <v>161.05</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE Nº.0014,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
+          <t>Referente a Anulação Total do saldo da NE Nº.0228,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos Ó</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2019NE00516</t>
+          <t>2019NE00395</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11868.84</v>
+        <v>1043.55</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Referente a Anulação Parcial do saldo da NE Nº.0149,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelos</t>
+          <t>Referente a Anulação Parcial do saldo da NE Nº.00304,para atender orientações contidas no Decreto nº.41.554,publicado no DOE em 26.11.2019,que dispõe sobre normas e procedimentos a serem adotados pelo</t>
         </is>
       </c>
     </row>
@@ -2634,21 +2634,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2023NE0000394</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2023NE0000396</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>26/09/2023</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>58671.87</v>
+        <v>156837.26</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2657,19 +2653,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2023NE0000395</t>
+          <t>2023NE0000393</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2678,7 +2674,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6147.75</v>
+        <v>503.24</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2687,19 +2683,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 011/2021 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2023NE0000393</t>
+          <t>2023NE0000395</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2708,7 +2704,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>503.24</v>
+        <v>6147.75</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2717,24 +2713,28 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 011/2021 AD: 01.</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2023NE0000396</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>2023NE0000394</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>26/09/2023</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>156837.26</v>
+        <v>58671.87</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
@@ -2810,12 +2810,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2020NE00233</t>
+          <t>2020NE00232</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>25221.28</v>
+        <v>33629</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2833,19 +2833,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Reforço da NE 028 para prestação Contratação para a prestação de serviços Técnicos em Informática.</t>
+          <t>Reforço da NE 29 para Serviços de Rede, Acesso Gerenciado à Internet, Disponibilização de Clientes VPN(Virtual Private Network),Serv.Eventuais de Informática e Hosp.de Servidor para o mes de junho 202</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020NE00232</t>
+          <t>2020NE00233</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>33629</v>
+        <v>25221.28</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2863,19 +2863,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Reforço da NE 29 para Serviços de Rede, Acesso Gerenciado à Internet, Disponibilização de Clientes VPN(Virtual Private Network),Serv.Eventuais de Informática e Hosp.de Servidor para o mes de junho 202</t>
+          <t>Reforço da NE 028 para prestação Contratação para a prestação de serviços Técnicos em Informática.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2024NE0000081</t>
+          <t>2024NE0000080</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10632.3</v>
+        <v>104174.06</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2893,19 +2893,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2024NE0000080</t>
+          <t>2024NE0000081</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>104174.06</v>
+        <v>10632.3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2982,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2022NE0000411</t>
+          <t>2022NE0000414</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12295.5</v>
+        <v>116181.92</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3005,19 +3005,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços Técnicos especializados em Inf., cont.os serv.de Exec.de Sist de Protocolo Web-Sproweb,exec.do Sist.de Rec.Humanos e Folha-Prodam-RH e Licença de usos do siste</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2022NE0000414</t>
+          <t>2022NE0000411</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>116181.92</v>
+        <v>12295.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3035,19 +3035,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Contratação para a prestação de serviços Técnicos especializados em Inf., cont.os serv.de Exec.de Sist de Protocolo Web-Sproweb,exec.do Sist.de Rec.Humanos e Folha-Prodam-RH e Licença de usos do siste</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2019NE00247</t>
+          <t>2019NE00250</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>2/2019</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2310.19</v>
+        <v>5933.28</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3065,19 +3065,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.0016, relativo ao 2º. Termo Aditivo ao Contrato nº.008/2016-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a prestação de serviços de Aces</t>
+          <t>Referente ao Reforço da NE nº.0046,relativo ao Termo de Contrato nº.002/2019-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2019NE00248</t>
+          <t>2019NE00249</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2416.5</v>
+        <v>7880.31</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3095,19 +3095,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº0047, relativo ao 5º.Termo Aditivo ao Contato nº.002/2015-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente ao Reforço da NE nº.0014,relativo ao 3º.Termo Aditivo ao Contº.nº.006/2015-PGE, celeb.entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2019NE00249</t>
+          <t>2019NE00248</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7880.31</v>
+        <v>2416.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3125,19 +3125,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0014,relativo ao 3º.Termo Aditivo ao Contº.nº.006/2015-PGE, celeb.entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente ao Reforço da NE nº0047, relativo ao 5º.Termo Aditivo ao Contato nº.002/2015-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2019NE00250</t>
+          <t>2019NE00247</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2/2019</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5933.28</v>
+        <v>2310.19</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0046,relativo ao Termo de Contrato nº.002/2019-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente ao Reforço da NE Nº.0016, relativo ao 2º. Termo Aditivo ao Contrato nº.008/2016-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a prestação de serviços de Aces</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2016NE00218</t>
+          <t>2016NE00217</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12049.62</v>
+        <v>6524.04</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Referente ao 5º. Termo Aditivo ao Contrato nº.04/2011-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A; Objeto:Prorrogar por 06(seis) meses,a prestação dos serviços Técnicos em</t>
+          <t>Objeto:Contratação para a prestação dos serviços de Execução de Sistemas Prodam-RH, para a PGE; Fundamentação Legal: Artº.24,Inciso XVI,da Lei nº.8.666/93, Parecer nº.889-AJUR/CGL e Portaria de Dispen</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2016NE00217</t>
+          <t>2016NE00218</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>6524.04</v>
+        <v>12049.62</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Objeto:Contratação para a prestação dos serviços de Execução de Sistemas Prodam-RH, para a PGE; Fundamentação Legal: Artº.24,Inciso XVI,da Lei nº.8.666/93, Parecer nº.889-AJUR/CGL e Portaria de Dispen</t>
+          <t>Referente ao 5º. Termo Aditivo ao Contrato nº.04/2011-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A; Objeto:Prorrogar por 06(seis) meses,a prestação dos serviços Técnicos em</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2019NE00143</t>
+          <t>2019NE00144</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7/2018</t>
+          <t>5/2018</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>748.2</v>
+        <v>8065.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.0020, relativo ao Termo de Contrato nº.007/2018-PGE.</t>
+          <t>Referente ao Reforço da NE nº.0018,relativo ao Termo de Contrato nº.005/2018-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2019NE00144</t>
+          <t>2019NE00143</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5/2018</t>
+          <t>7/2018</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>8065.5</v>
+        <v>748.2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3391,17 +3391,21 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0018,relativo ao Termo de Contrato nº.005/2018-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente ao Reforço da NE Nº.0020, relativo ao Termo de Contrato nº.007/2018-PGE.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2016NE00319</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>2016NE00320</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2/2015</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>22/11/2016</t>
@@ -3417,19 +3421,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cancelamento da NE nº.0318, para fazer a NE de reforço</t>
+          <t>Objeto:Referente ao reforço da NE nº.0033, para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança; Fundamentação Legal:Artº.24,</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2016NE00321</t>
+          <t>2016NE00322</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3438,7 +3442,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>38264.57</v>
+        <v>1497.6</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3447,7 +3451,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objeto:Referente ao reforço da NE nº.0252,para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, compreendendo o fornecimento de infraestrutura de TI, para a Hospedagem </t>
+          <t>Objeto:Referente ao reforço da NE nº.0271,para a prestação dos serviços Eventuais de Informática, para a PGE; Fundamentação Legal:Parecer nº.1.107/2014-ASS/CGL,Ata de Registro de Dispensa de Licitação</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3488,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2016NE00322</t>
+          <t>2016NE00321</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3498,7 +3502,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1497.6</v>
+        <v>38264.57</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3507,21 +3511,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Objeto:Referente ao reforço da NE nº.0271,para a prestação dos serviços Eventuais de Informática, para a PGE; Fundamentação Legal:Parecer nº.1.107/2014-ASS/CGL,Ata de Registro de Dispensa de Licitação</t>
+          <t xml:space="preserve">Objeto:Referente ao reforço da NE nº.0252,para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, compreendendo o fornecimento de infraestrutura de TI, para a Hospedagem </t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2016NE00320</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2/2015</t>
-        </is>
-      </c>
+          <t>2016NE00319</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>22/11/2016</t>
@@ -3537,14 +3537,14 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Objeto:Referente ao reforço da NE nº.0033, para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança; Fundamentação Legal:Artº.24,</t>
+          <t>Cancelamento da NE nº.0318, para fazer a NE de reforço</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2025NE0000420</t>
+          <t>2025NE0000421</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>71.72</v>
+        <v>201539.05</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Anulação de saldo da NE 09/2025por fim de prazo do 7º Termo aditivo ao contrato nº 06/2019 -PGE</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2025NE0000421</t>
+          <t>2025NE0000420</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>201539.05</v>
+        <v>71.72</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Anulação de saldo da NE 09/2025por fim de prazo do 7º Termo aditivo ao contrato nº 06/2019 -PGE</t>
         </is>
       </c>
     </row>
@@ -3648,17 +3648,21 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2025NE0000183</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>2025NE0000181</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>13/2024</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>22/05/2025</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>174667.18</v>
+        <v>15214.86</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3667,28 +3671,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025NE0000181</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>13/2024</t>
-        </is>
-      </c>
+          <t>2025NE0000183</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
           <t>22/05/2025</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>15214.86</v>
+        <v>174667.18</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2019NE00138</t>
+          <t>2019NE00137</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>7880.31</v>
+        <v>2416.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3757,19 +3757,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0014,relativo ao 3º.Termo Aditivo ao Contrato nº.006/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente ao Reforço da NE nº.0047, relativo ao 5º. Termo Aditivo ao Contrato nº.02/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2019NE00141</t>
+          <t>2019NE00139</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>40234.67</v>
+        <v>12240</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0019,relativo ao 7º. Termo Aditivo ao Contrato nº.007/2014-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente ao Reforço da NE nº.0016, relativo ao 2º. Termo Aditivo ao Contrato nº.008/2016-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2019NE00139</t>
+          <t>2019NE00141</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>12240</v>
+        <v>40234.67</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3847,19 +3847,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0016, relativo ao 2º. Termo Aditivo ao Contrato nº.008/2016-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A</t>
+          <t>Referente ao Reforço da NE nº.0019,relativo ao 7º. Termo Aditivo ao Contrato nº.007/2014-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2019NE00137</t>
+          <t>2019NE00138</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2416.5</v>
+        <v>7880.31</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0047, relativo ao 5º. Termo Aditivo ao Contrato nº.02/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente ao Reforço da NE nº.0014,relativo ao 3º.Termo Aditivo ao Contrato nº.006/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
@@ -4000,17 +4000,21 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2024NE0000200</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>2024NE0000201</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>12/2019</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
           <t>20/05/2024</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10632.3</v>
+        <v>24591</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4019,7 +4023,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Referente a Anulação do saldo da NE Nº.0081,no valor de R$10.632,30,relativo ao 5°. Termo Aditivo ao Contrato nº.012/2019-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, não</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
@@ -4052,21 +4056,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2024NE0000201</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>12/2019</t>
-        </is>
-      </c>
+          <t>2024NE0000200</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>20/05/2024</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>24591</v>
+        <v>10632.3</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4075,28 +4075,24 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Referente a Anulação do saldo da NE Nº.0081,no valor de R$10.632,30,relativo ao 5°. Termo Aditivo ao Contrato nº.012/2019-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, não</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2023NE00238</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2023NE0000238</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>19/07/2023</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>309.83</v>
+        <v>890.74</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4105,24 +4101,28 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cobertura Financeira</t>
+          <t>Referente a Anulação Parcial da NE nº.0224/2023, referente ao 5º. Termo Aditivo ao Contrato nº.006/2019-PGE, para ajuste no valor mensal que de R$58.671,87, reduz para R$58.090,96, conforme Diraf 208/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2023NE0000238</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>2023NE00238</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
           <t>19/07/2023</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>890.74</v>
+        <v>309.83</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4131,17 +4131,21 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Referente a Anulação Parcial da NE nº.0224/2023, referente ao 5º. Termo Aditivo ao Contrato nº.006/2019-PGE, para ajuste no valor mensal que de R$58.671,87, reduz para R$58.090,96, conforme Diraf 208/</t>
+          <t>Cobertura Financeira</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2019NE00226</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>2019NE00225</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
           <t>19/07/2019</t>
@@ -4157,19 +4161,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº0225,relativo ao Termo de Contrato nº.006/2019-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede, comp.o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),S</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2019NE00229</t>
+          <t>2019NE00223</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7/2018</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4178,7 +4182,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>522.12</v>
+        <v>19089.84</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4187,24 +4191,28 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de Licenciamento de Uso do INTEGRA perfil Intermediário para a PGE.</t>
+          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede, comp.o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),S</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2019NE00224</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>2019NE00228</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>19/07/2019</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>19089.84</v>
+        <v>17621.39</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4213,7 +4221,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Anulação da NE nº.0223,relativa ao Termo de Contrato nº.006/2019-PGE, para acerto no prazo de vigência.</t>
+          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede,como o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),Se</t>
         </is>
       </c>
     </row>
@@ -4250,21 +4258,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2019NE00228</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2019NE00224</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>19/07/2019</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>17621.39</v>
+        <v>19089.84</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4273,19 +4277,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede,como o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),Se</t>
+          <t>Anulação da NE nº.0223,relativa ao Termo de Contrato nº.006/2019-PGE, para acerto no prazo de vigência.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2019NE00223</t>
+          <t>2019NE00229</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>7/2018</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4294,7 +4298,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>19089.84</v>
+        <v>522.12</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4303,21 +4307,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede, comp.o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),S</t>
+          <t>Contratação para a prestação de serviços de Licenciamento de Uso do INTEGRA perfil Intermediário para a PGE.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2019NE00225</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2019NE00226</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
           <t>19/07/2019</t>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede, comp.o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),S</t>
+          <t>Anulação da NE Nº0225,relativo ao Termo de Contrato nº.006/2019-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2014NE00072</t>
+          <t>2014NE00255</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>91946.89</v>
+        <v>135686.31</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2014NE00255</t>
+          <t>2014NE00072</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>135686.31</v>
+        <v>91946.89</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2016NE00314</t>
+          <t>2016NE00311</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1052.14</v>
+        <v>1304.7</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4539,19 +4539,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Objeto:Prorrogar o prazo de vigência por 12(doze) meses e reajustar o valor do Termo de Contrato nº.006/2015-PGE em 11,65%, com base no IGPM do período; Fundamentação Legal:Artº.24, Inciso XVI, da Lei</t>
+          <t>Objeto:Referente ao reforço da NE nº.0027, para a prestação dos serviços de Execução de Sistemas Prodam-RH, para a PGE; Fundamentação Legal:Artº.24,Inciso XVI da Lei nº.8.666/93,Parecer nº.889-AJUR/CG</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2016NE00312</t>
+          <t>2016NE00313</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2409.91</v>
+        <v>1768</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4569,19 +4569,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Objeto:Referente ao reforço da NE nº.0186,para a prestação dos serviços Técnicos em Telecomunicações para a Rede Mundial Internet em 1,5 MBps,estabelecendo comunicação a partir do link ótico ponto-a-p</t>
+          <t>Objeto:Prestação dos serviços de rede compreendendo o Acesso Gerenciado à Internet,através da Rede de Governo; Fundamentação Legal:Dispensa de Licitação baseada na Lei nº.8.666/93, artº.24, inciso XVI</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2016NE00313</t>
+          <t>2016NE00312</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1768</v>
+        <v>2409.91</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4599,14 +4599,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Objeto:Prestação dos serviços de rede compreendendo o Acesso Gerenciado à Internet,através da Rede de Governo; Fundamentação Legal:Dispensa de Licitação baseada na Lei nº.8.666/93, artº.24, inciso XVI</t>
+          <t>Objeto:Referente ao reforço da NE nº.0186,para a prestação dos serviços Técnicos em Telecomunicações para a Rede Mundial Internet em 1,5 MBps,estabelecendo comunicação a partir do link ótico ponto-a-p</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2016NE00311</t>
+          <t>2016NE00314</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1304.7</v>
+        <v>1052.14</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Objeto:Referente ao reforço da NE nº.0027, para a prestação dos serviços de Execução de Sistemas Prodam-RH, para a PGE; Fundamentação Legal:Artº.24,Inciso XVI da Lei nº.8.666/93,Parecer nº.889-AJUR/CG</t>
+          <t>Objeto:Prorrogar o prazo de vigência por 12(doze) meses e reajustar o valor do Termo de Contrato nº.006/2015-PGE em 11,65%, com base no IGPM do período; Fundamentação Legal:Artº.24, Inciso XVI, da Lei</t>
         </is>
       </c>
     </row>
@@ -4666,12 +4666,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2023NE0000162</t>
+          <t>2023NE0000161</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>12295.5</v>
+        <v>1006.48</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4689,19 +4689,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 011/2021 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2023NE0000161</t>
+          <t>2023NE0000162</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1006.48</v>
+        <v>12295.5</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4719,14 +4719,14 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 011/2021 AD: 01.</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2014NE00041</t>
+          <t>2014NE00040</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1267</v>
+        <v>3801.03</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2014NE00040</t>
+          <t>2014NE00041</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>3801.03</v>
+        <v>1267</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -4789,11 +4789,7 @@
           <t>2016NE00205</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>9/2016</t>
-        </is>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>16/12/2016</t>
@@ -4819,7 +4815,11 @@
           <t>2016NE00205</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>9/2016</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
           <t>16/12/2016</t>
@@ -4932,21 +4932,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025NE0000356</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>13/2024</t>
-        </is>
-      </c>
+          <t>2025NE0000357</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
           <t>16/09/2025</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>7607.43</v>
+        <v>201539.05</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -4955,24 +4951,28 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2025NE0000357</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
+          <t>2025NE0000356</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>13/2024</t>
+        </is>
+      </c>
       <c r="C157" t="inlineStr">
         <is>
           <t>16/09/2025</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>201539.05</v>
+        <v>7607.43</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
         </is>
       </c>
     </row>
@@ -5138,21 +5138,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2025NE0000168</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>11/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000164</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
           <t>16/05/2025</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1250</v>
+        <v>211180.42</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5161,24 +5157,28 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 03.</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025NE0000164</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>2025NE0000168</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>11/2021</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr">
         <is>
           <t>16/05/2025</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>211180.42</v>
+        <v>1250</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 03.</t>
         </is>
       </c>
     </row>
@@ -5254,12 +5254,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2024NE0000427</t>
+          <t>2024NE0000426</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>86052.06</v>
+        <v>5533.02</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5277,19 +5277,19 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2024NE0000426</t>
+          <t>2024NE0000427</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>5533.02</v>
+        <v>86052.06</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
@@ -5317,11 +5317,7 @@
           <t>2019NE00282</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
           <t>15/10/2019</t>
@@ -5377,7 +5373,11 @@
           <t>2019NE00282</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C171" t="inlineStr">
         <is>
           <t>15/10/2019</t>
@@ -5400,7 +5400,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2019NE00151</t>
+          <t>2019NE00149</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>103268.89</v>
+        <v>220267.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5423,14 +5423,14 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Contratação referente a prestação de serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica no Data Center da Prodam.</t>
+          <t>Contratação para a prestação de serviços técnicos especializados em informática,contemplando os serv.de Rede,compreendendo o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN,Serv.Even</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2019NE00149</t>
+          <t>2019NE00151</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>220267.4</v>
+        <v>103268.89</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços técnicos especializados em informática,contemplando os serv.de Rede,compreendendo o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN,Serv.Even</t>
+          <t>Contratação referente a prestação de serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica no Data Center da Prodam.</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2018NE00416</t>
+          <t>2018NE00418</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6120</v>
+        <v>10336</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5599,19 +5599,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Contratação para prestação dos serviços de Acesso Gerenciado à Internet, através da Rede de Governo.</t>
+          <t>Referente ao Reforço da NE Nº.0186,para a prestação dos serviços de Acesso Gerenciado a Internet,através da Rede de Governo, conf.1º.Termo Aditivo ao Contº.nº.008/2016-PGE.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2018NE00415</t>
+          <t>2018NE00417</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>3940.16</v>
+        <v>742.26</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5629,19 +5629,19 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Contratação para prestação de serviços de Execução do Sistema PRODAM RH.</t>
+          <t>Referente ao Reforço da NE Nº.0188, para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam,com Serviços de Backup e Segurança,conforme 4º.Termo Aditivo ao Contrato</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2018NE00417</t>
+          <t>2018NE00415</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5650,7 +5650,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>742.26</v>
+        <v>3940.16</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -5659,14 +5659,14 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.0188, para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam,com Serviços de Backup e Segurança,conforme 4º.Termo Aditivo ao Contrato</t>
+          <t>Contratação para prestação de serviços de Execução do Sistema PRODAM RH.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2018NE00418</t>
+          <t>2018NE00416</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>10336</v>
+        <v>6120</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.0186,para a prestação dos serviços de Acesso Gerenciado a Internet,através da Rede de Governo, conf.1º.Termo Aditivo ao Contº.nº.008/2016-PGE.</t>
+          <t>Contratação para prestação dos serviços de Acesso Gerenciado à Internet, através da Rede de Governo.</t>
         </is>
       </c>
     </row>
@@ -6081,11 +6081,7 @@
           <t>2015NE00190</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>6/2015</t>
-        </is>
-      </c>
+      <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
           <t>12/11/2015</t>
@@ -6137,7 +6133,11 @@
           <t>2015NE00190</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>6/2015</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
           <t>12/11/2015</t>
@@ -6220,7 +6220,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2019NE00080</t>
+          <t>2019NE00079</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6243,14 +6243,14 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ref. ao pagto. de Despesa de Exercícios Anteriores,pela prestação de Serviços de Hospedagem do Site da PGE, no mês de Novembro/2018, conf. NFS-e nº.4916 emitida em 21.11.2018 e 4º.Termo Aditivo ao Con</t>
+          <t>Ref. ao pagto. de Despesa de Exercícios Anteriores,pela prestação de Serviços de Hospedagem do Site da PGE, no mês de Dezembro/2018, conf. NFS-e nº.5560 emitida em 06.12.2018 e 4º.Termo Aditivo ao Con</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2019NE00079</t>
+          <t>2019NE00080</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ref. ao pagto. de Despesa de Exercícios Anteriores,pela prestação de Serviços de Hospedagem do Site da PGE, no mês de Dezembro/2018, conf. NFS-e nº.5560 emitida em 06.12.2018 e 4º.Termo Aditivo ao Con</t>
+          <t>Ref. ao pagto. de Despesa de Exercícios Anteriores,pela prestação de Serviços de Hospedagem do Site da PGE, no mês de Novembro/2018, conf. NFS-e nº.4916 emitida em 21.11.2018 e 4º.Termo Aditivo ao Con</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2025NE0000266</t>
+          <t>2025NE0000265</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6340,7 +6340,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2025NE0000265</t>
+          <t>2025NE0000266</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6370,21 +6370,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2022NE0000384</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>11/2021</t>
-        </is>
-      </c>
+          <t>2022NE0000383</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
           <t>10/11/2022</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>251.62</v>
+        <v>3000</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6393,24 +6389,28 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE.</t>
+          <t>Referente a Anulação parcial da NE Nº.0027, relativo ao Termo de Contrato nº.011/2021-PGE</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2022NE0000383</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr"/>
+          <t>2022NE0000384</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>11/2021</t>
+        </is>
+      </c>
       <c r="C206" t="inlineStr">
         <is>
           <t>10/11/2022</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>3000</v>
+        <v>251.62</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6419,24 +6419,28 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Referente a Anulação parcial da NE Nº.0027, relativo ao Termo de Contrato nº.011/2021-PGE</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025NE0000259</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
+          <t>2025NE0000257</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C207" t="inlineStr">
         <is>
           <t>10/07/2025</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>403078.1</v>
+        <v>412000</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6445,28 +6449,24 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para a prestação de serviços de Acesso Gerenciado à Internet, VPN(Virtual Private Network, Eventuais de Informática, Hospedagem de Sistemas de Execução Fiscal EletrÔnica. TC: 0006/2019 AD:</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025NE0000257</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2025NE0000259</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
           <t>10/07/2025</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>412000</v>
+        <v>403078.1</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6475,24 +6475,28 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de Acesso Gerenciado à Internet, VPN(Virtual Private Network, Eventuais de Informática, Hospedagem de Sistemas de Execução Fiscal EletrÔnica. TC: 0006/2019 AD:</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2024NE0000275</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
+          <t>2024NE0000276</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>12/2019</t>
+        </is>
+      </c>
       <c r="C209" t="inlineStr">
         <is>
           <t>10/07/2024</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>338792.14</v>
+        <v>5316.15</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6501,14 +6505,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2024NE0000273</t>
+          <t>2024NE0000274</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6522,7 +6526,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>49250</v>
+        <v>10000</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -6538,7 +6542,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2024NE0000274</t>
+          <t>2024NE0000273</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6552,7 +6556,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>10000</v>
+        <v>49250</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -6568,21 +6572,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2024NE0000276</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>12/2019</t>
-        </is>
-      </c>
+          <t>2024NE0000275</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
           <t>10/07/2024</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>5316.15</v>
+        <v>338792.14</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -6591,19 +6591,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2025NE0000085</t>
+          <t>2025NE0000086</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>13/2024</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1250</v>
+        <v>15214.86</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6621,19 +6621,19 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 03.</t>
+          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2025NE0000086</t>
+          <t>2025NE0000085</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>13/2024</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>15214.86</v>
+        <v>1250</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6651,14 +6651,14 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2019NE00256</t>
+          <t>2019NE00255</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -6668,7 +6668,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>7387.25</v>
+        <v>2900.5</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Referente a Anulação do saldo da NE nº.0204,por motivo de término do contrato nº.005/2018-PGE ,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a prestação de serviços de Exe</t>
+          <t>Referente a Anulação do saldo da NE nº.0015, por motivo de Distrato ao Contrato nº.012/2014-PGE; Relativo ao 6º.Termo Aditivo ao Contrato nº.012/2014-PGE, celebrado entre a PGE e a Prodam Processament</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2019NE00255</t>
+          <t>2019NE00256</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>2900.5</v>
+        <v>7387.25</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -6703,14 +6703,14 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Referente a Anulação do saldo da NE nº.0015, por motivo de Distrato ao Contrato nº.012/2014-PGE; Relativo ao 6º.Termo Aditivo ao Contrato nº.012/2014-PGE, celebrado entre a PGE e a Prodam Processament</t>
+          <t>Referente a Anulação do saldo da NE nº.0204,por motivo de término do contrato nº.005/2018-PGE ,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para a prestação de serviços de Exe</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2024NE0000271</t>
+          <t>2024NE0000270</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>62968.24</v>
+        <v>5316.15</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -6729,14 +6729,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total da NE Nº.016,pelo saldo não liquidado até Junho/2024.</t>
+          <t>Referente a Anulação da NE nº.057, pelo motivo da não assinatura do Termo Aditivo de Redução.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2024NE0000270</t>
+          <t>2024NE0000271</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>5316.15</v>
+        <v>62968.24</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6755,19 +6755,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Referente a Anulação da NE nº.057, pelo motivo da não assinatura do Termo Aditivo de Redução.</t>
+          <t>Referente a Anulação Total da NE Nº.016,pelo saldo não liquidado até Junho/2024.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2024NE0000484</t>
+          <t>2024NE0000475</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>13/2024</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6776,7 +6776,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>19975.6</v>
+        <v>546000</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
@@ -6818,12 +6818,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2024NE0000475</t>
+          <t>2024NE0000484</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>13/2024</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>546000</v>
+        <v>19975.6</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
         </is>
       </c>
     </row>
@@ -6904,17 +6904,21 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2024NE0000100</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr"/>
+          <t>2024NE0000099</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>11/2021</t>
+        </is>
+      </c>
       <c r="C224" t="inlineStr">
         <is>
           <t>08/03/2024</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>345041.98</v>
+        <v>1006.48</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -6923,28 +6927,24 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2024NE0000099</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>11/2021</t>
-        </is>
-      </c>
+          <t>2024NE0000100</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
           <t>08/03/2024</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1006.48</v>
+        <v>345041.98</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7042,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2023NE00224</t>
+          <t>2023NE0000224</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Prorrogação de prazo</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2023NE0000224</t>
+          <t>2023NE00224</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Prorrogação de prazo</t>
         </is>
       </c>
     </row>
@@ -7162,17 +7162,21 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2024NE0000179</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr"/>
+          <t>2024NE0000180</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>11/2021</t>
+        </is>
+      </c>
       <c r="C233" t="inlineStr">
         <is>
           <t>06/05/2024</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>195523.79</v>
+        <v>1006.48</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7181,28 +7185,24 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2024NE0000180</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>11/2021</t>
-        </is>
-      </c>
+          <t>2024NE0000179</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="inlineStr">
         <is>
           <t>06/05/2024</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1006.48</v>
+        <v>195523.79</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2022NE0000334</t>
+          <t>2022NE00334</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7271,14 +7271,14 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Reajuste de 25%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2022NE00334</t>
+          <t>2022NE0000334</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Reajuste de 25%</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
@@ -7334,12 +7334,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2022NE0000293</t>
+          <t>2022NE0000294</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>11197.06</v>
+        <v>92945.53999999999</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7357,19 +7357,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.028,relativo ao 2º. Termo Aditivo ao Contrato nº.012/2019-PGE.</t>
+          <t>Referente ao Reforço da NE Nº.0239, relativo ao 3º.Termo Aditivo ao Contrato nº.006/2019-PGE.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2022NE0000294</t>
+          <t>2022NE0000293</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>92945.53999999999</v>
+        <v>11197.06</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7387,14 +7387,14 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.0239, relativo ao 3º.Termo Aditivo ao Contrato nº.006/2019-PGE.</t>
+          <t>Referente ao Reforço da NE Nº.028,relativo ao 2º. Termo Aditivo ao Contrato nº.012/2019-PGE.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2025NE00315</t>
+          <t>2025NE0000315</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7417,14 +7417,14 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Serviços de Informática</t>
+          <t>Contratação para a prestação de serviços de Acesso Gerenciado à Internet, VPN, Eventuais de Informática e Hospedagem de Sistema de Execução Fiscal Eletrônica.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2025NE0000315</t>
+          <t>2025NE00315</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de Acesso Gerenciado à Internet, VPN, Eventuais de Informática e Hospedagem de Sistema de Execução Fiscal Eletrônica.</t>
+          <t>Serviços de Informática</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2023NE0000221</t>
+          <t>2023NE0000220</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1006.48</v>
+        <v>12295.5</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7507,19 +7507,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 011/2021 AD: 01.</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2023NE0000220</t>
+          <t>2023NE0000221</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>12295.5</v>
+        <v>1006.48</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7537,19 +7537,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 011/2021 AD: 01.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2014NE00167</t>
+          <t>2014NE00166</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>10449.65</v>
+        <v>29588.53</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7567,19 +7567,19 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Contrato No. 5/2010 - CFPP - Cadastro Folha de Pagto de Pessoal</t>
+          <t>Contrato No. 4/2011 - Acesso … Internet 1,5 Mbps</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2014NE00166</t>
+          <t>2014NE00167</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>29588.53</v>
+        <v>10449.65</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7597,28 +7597,24 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Contrato No. 4/2011 - Acesso … Internet 1,5 Mbps</t>
+          <t>Contrato No. 5/2010 - CFPP - Cadastro Folha de Pagto de Pessoal</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026NE0000004</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>13/2024</t>
-        </is>
-      </c>
+          <t>2026NE0000031</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>30429.72</v>
+        <v>806156.2</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7627,7 +7623,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7660,21 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026NE0000031</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr"/>
+          <t>2026NE0000004</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>13/2024</t>
+        </is>
+      </c>
       <c r="C250" t="inlineStr">
         <is>
           <t>05/01/2026</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>806156.2</v>
+        <v>30429.72</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7683,19 +7683,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t xml:space="preserve">Contratação para a prestação de serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha -PRODAM-RH e Licença de usos do Sistema de </t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2015NE00002</t>
+          <t>2015NE00031</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>7800</v>
+        <v>121569.39</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7713,19 +7713,19 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Cobertura Financeira jan a mar 2015</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2015NE00021</t>
+          <t>2015NE00028</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>7800</v>
+        <v>70801.17</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7743,19 +7743,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015</t>
+          <t>Anulação total da NE 022/2015 para acerto no valor mensal contratado.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2015NE00006</t>
+          <t>2015NE00022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>4274.85</v>
+        <v>70801.17</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015</t>
+          <t>Contratação para Hospedagem de Sistemas compreendendo fornecimento de Infraestrutura de TI para Hospedagem do Sistema PGEnet, no Data Center da PRODAM.</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2015NE00022</t>
+          <t>2015NE00006</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>70801.17</v>
+        <v>4274.85</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7833,19 +7833,19 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Contratação para Hospedagem de Sistemas compreendendo fornecimento de Infraestrutura de TI para Hospedagem do Sistema PGEnet, no Data Center da PRODAM.</t>
+          <t>Cobertura financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2015NE00028</t>
+          <t>2015NE00021</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>70801.17</v>
+        <v>7800</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7863,19 +7863,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Anulação total da NE 022/2015 para acerto no valor mensal contratado.</t>
+          <t>Cobertura financeira 2015</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2015NE00031</t>
+          <t>2015NE00002</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>121569.39</v>
+        <v>7800</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Cobertura Financeira jan a mar 2015</t>
         </is>
       </c>
     </row>
@@ -7926,12 +7926,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2021NE0000032</t>
+          <t>2021NE0000029</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>25221.28</v>
+        <v>176213.92</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -7949,19 +7949,19 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Contratação para a prest.de Serviços Tecnicos Especializados em Informática,contemp.os Serviços de Exec.do Sist.de Protocolo Web-SPROWEB,e Exec.do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licen</t>
+          <t>ServiçosTécnicos Especializados em Informática,contemplando Serviços de Rede, Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),Serviços Eventuais de Informáti</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2021NE0000029</t>
+          <t>2021NE0000032</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>176213.92</v>
+        <v>25221.28</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -7979,19 +7979,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>ServiçosTécnicos Especializados em Informática,contemplando Serviços de Rede, Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),Serviços Eventuais de Informáti</t>
+          <t>Contratação para a prest.de Serviços Tecnicos Especializados em Informática,contemp.os Serviços de Exec.do Sist.de Protocolo Web-SPROWEB,e Exec.do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licen</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2016NE00029</t>
+          <t>2016NE00030</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8000,7 +8000,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>206667.96</v>
+        <v>623.28</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8009,19 +8009,19 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Objeto:Contratação para prorrogar por 12(doze) meses, a prestação dos serviços de Hospedagem do Sistema,compreendendo o fornecimento de infraestrutura de TI, para a Hospedagem do Sistema PGE.net,no Da</t>
+          <t>Objeto:Contratação para a prestação dos serviços de Hospedagem do Site, contemplando a disponibilidade dos recursos necessários para hospedagem do site na infraestrutura tecnológica da Prodam, com ser</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2016NE00031</t>
+          <t>2016NE00027</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>8088.6</v>
+        <v>13048.08</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8039,19 +8039,19 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objeto:Contratação para prorrogar a vigência por 12(doze) meses,da prestação dos serviços Técnicos em Informática de Forma Eventual,para a PGE; Fundamentação Legal:Parecer nº.1107/2014-ASS/CGL,Ata de </t>
+          <t>Objeto:Contratação para a prestação dos serviços de Execução de Sistemas Prodam-RH, para a PGE; Fundamentação Legal: Atº. 24, Inciso XVI, da Lei nº.8.666/93, Parecer nº.889-AJUR/CGL e Portaria de Disp</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2016NE00033</t>
+          <t>2016NE00028</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>3430.85</v>
+        <v>18476.1</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8069,19 +8069,19 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Objeto: Prorrogação do prazo de vigência do contrato original por mais 12(doze) meses, a contar da data de sua assinatura, conforme cláusula oitava do contrato e reajustar, com base no IGPM, em 10,09%</t>
+          <t>Objeto:Contratação para prorrogar por 12(doze) meses, a prestação dos serviços Técnicos em Telecomunicações para a Rede Mundial Internet em 1,5 MBps, estabelecendo comunicação a partir do link ótico p</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2016NE00028</t>
+          <t>2016NE00033</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>18476.1</v>
+        <v>3430.85</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8099,19 +8099,19 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Objeto:Contratação para prorrogar por 12(doze) meses, a prestação dos serviços Técnicos em Telecomunicações para a Rede Mundial Internet em 1,5 MBps, estabelecendo comunicação a partir do link ótico p</t>
+          <t>Objeto: Prorrogação do prazo de vigência do contrato original por mais 12(doze) meses, a contar da data de sua assinatura, conforme cláusula oitava do contrato e reajustar, com base no IGPM, em 10,09%</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2016NE00027</t>
+          <t>2016NE00031</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>13048.08</v>
+        <v>8088.6</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8129,19 +8129,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Objeto:Contratação para a prestação dos serviços de Execução de Sistemas Prodam-RH, para a PGE; Fundamentação Legal: Atº. 24, Inciso XVI, da Lei nº.8.666/93, Parecer nº.889-AJUR/CGL e Portaria de Disp</t>
+          <t xml:space="preserve">Objeto:Contratação para prorrogar a vigência por 12(doze) meses,da prestação dos serviços Técnicos em Informática de Forma Eventual,para a PGE; Fundamentação Legal:Parecer nº.1107/2014-ASS/CGL,Ata de </t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2016NE00030</t>
+          <t>2016NE00029</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>623.28</v>
+        <v>206667.96</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Objeto:Contratação para a prestação dos serviços de Hospedagem do Site, contemplando a disponibilidade dos recursos necessários para hospedagem do site na infraestrutura tecnológica da Prodam, com ser</t>
+          <t>Objeto:Contratação para prorrogar por 12(doze) meses, a prestação dos serviços de Hospedagem do Sistema,compreendendo o fornecimento de infraestrutura de TI, para a Hospedagem do Sistema PGE.net,no Da</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2022NE0000332</t>
+          <t>2022NE0000333</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>7974.92</v>
+        <v>4000</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8211,14 +8211,14 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total da NE nº.0020, por término da vigência do 2º. Termo Aditivo ao Contrato nº.006/2019-PGE.</t>
+          <t>Referente a Anulação Parcial da NE Nº.0028, no valor de R$4.000,00(Quatro mil Reais), pelo motivo de que, o saldo de valores já pagos do período de Janeiro à Agosto/2022.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2022NE0000333</t>
+          <t>2022NE0000332</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>4000</v>
+        <v>7974.92</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8237,14 +8237,14 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Referente a Anulação Parcial da NE Nº.0028, no valor de R$4.000,00(Quatro mil Reais), pelo motivo de que, o saldo de valores já pagos do período de Janeiro à Agosto/2022.</t>
+          <t>Referente a Anulação Total da NE nº.0020, por término da vigência do 2º. Termo Aditivo ao Contrato nº.006/2019-PGE.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2016NE00294</t>
+          <t>2016NE00291</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>38264.57</v>
+        <v>2174.68</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0252.</t>
+          <t>Referente ao reforço da NE nº.0027.</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2016NE00292</t>
+          <t>2016NE00294</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>4016.54</v>
+        <v>38264.57</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8315,14 +8315,14 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE Nº.0186.</t>
+          <t>Referente ao reforço da NE nº.0252.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2016NE00292</t>
+          <t>2016NE00295</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>4016.54</v>
+        <v>1497.6</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE Nº.0186.</t>
+          <t>Referente ao reforço da NE nº.0271.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2016NE00295</t>
+          <t>2016NE00291</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1497.6</v>
+        <v>2174.68</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8367,14 +8367,14 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0271.</t>
+          <t>Referente ao reforço da NE nº.0027.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2016NE00291</t>
+          <t>2016NE00295</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>2174.68</v>
+        <v>1497.6</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -8393,14 +8393,14 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0027.</t>
+          <t>Referente ao reforço da NE nº.0271.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2016NE00295</t>
+          <t>2016NE00292</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1497.6</v>
+        <v>4016.54</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -8419,14 +8419,14 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0271.</t>
+          <t>Referente ao reforço da NE Nº.0186.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2016NE00294</t>
+          <t>2016NE00292</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>38264.57</v>
+        <v>4016.54</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0252.</t>
+          <t>Referente ao reforço da NE Nº.0186.</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2016NE00291</t>
+          <t>2016NE00294</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>2174.68</v>
+        <v>38264.57</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -8497,19 +8497,19 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0027.</t>
+          <t>Referente ao reforço da NE nº.0252.</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2018NE00341</t>
+          <t>2018NE00358</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>40234.67</v>
+        <v>587</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Prodam.</t>
+          <t>Referente ao Reforço da NE nº.0183,para complementar recursos objetivando o pagamento da prestação dos serviços executados pela Prodam,no mês de Agôsto/2017,conf.NFS-e nº.3377/2018, no valor de R$1.11</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8564,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2018NE00358</t>
+          <t>2018NE00341</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>587</v>
+        <v>40234.67</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8587,19 +8587,19 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0183,para complementar recursos objetivando o pagamento da prestação dos serviços executados pela Prodam,no mês de Agôsto/2017,conf.NFS-e nº.3377/2018, no valor de R$1.11</t>
+          <t>Contratação para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Prodam.</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2017NE00083</t>
+          <t>2017NE00093</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>2985.92</v>
+        <v>16320</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8617,19 +8617,19 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.036, relativa ao 3º. Termo Aditivo ao Contrato nº.02/2015-PGE.</t>
+          <t>Referente ao Reforço da NE nº.0021, relativa ao Termo de Contrato nº.008/2016-PGE</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2017NE00090</t>
+          <t>2017NE00087</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>9712.120000000001</v>
+        <v>27746.12</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.023,relativa ao 1º. Termo Aditivo ao Contrato nº.006/2015-PGE.</t>
+          <t>Referente ao Reforço da NE nº.022, relativa ao Termo de Contrato nº.09/2016-PGE.</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8684,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2017NE00087</t>
+          <t>2017NE00090</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>27746.12</v>
+        <v>9712.120000000001</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8707,19 +8707,19 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.022, relativa ao Termo de Contrato nº.09/2016-PGE.</t>
+          <t>Referente ao Reforço da NE nº.023,relativa ao 1º. Termo Aditivo ao Contrato nº.006/2015-PGE.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2017NE00093</t>
+          <t>2017NE00083</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>16320</v>
+        <v>2985.92</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8737,19 +8737,19 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0021, relativa ao Termo de Contrato nº.008/2016-PGE</t>
+          <t>Referente ao Reforço da NE nº.036, relativa ao 3º. Termo Aditivo ao Contrato nº.02/2015-PGE.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2022NE0000027</t>
+          <t>2022NE0000028</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>2/2019</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8758,7 +8758,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>4547.32</v>
+        <v>23166.32</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -8767,19 +8767,19 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de Cerificação Digital.</t>
+          <t>Contratação para a prestação de serviços Técnicos especializados em Inf., cont.os serv.de Exec.de Sist de Protocolo Web-Sproweb,exec.do Sist.de Rec.Humanos e Folha-Prodam-RH e Licença de usos do siste</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2022NE0000028</t>
+          <t>2022NE0000027</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2/2019</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>23166.32</v>
+        <v>4547.32</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços Técnicos especializados em Inf., cont.os serv.de Exec.de Sist de Protocolo Web-Sproweb,exec.do Sist.de Rec.Humanos e Folha-Prodam-RH e Licença de usos do siste</t>
+          <t>Contratação para a prestação de serviços de Cerificação Digital.</t>
         </is>
       </c>
     </row>
@@ -8912,12 +8912,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2018NE00199</t>
+          <t>2018NE00200</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>73993.08</v>
+        <v>8160</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -8935,19 +8935,19 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
+          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2018NE00198</t>
+          <t>2018NE00201</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8956,7 +8956,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>1485</v>
+        <v>2356.14</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
+          <t>Contratação para a prestação de serviços Eventuais de Informática</t>
         </is>
       </c>
     </row>
@@ -9002,12 +9002,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2018NE00201</t>
+          <t>2018NE00198</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9016,7 +9016,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2356.14</v>
+        <v>1485</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9025,19 +9025,19 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços Eventuais de Informática</t>
+          <t>Contratação para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2018NE00200</t>
+          <t>2018NE00199</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>8160</v>
+        <v>73993.08</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9055,19 +9055,19 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
+          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2015NE00091</t>
+          <t>2015NE00090</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>8033.08</v>
+        <v>1801.28</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9085,14 +9085,14 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.015/2015; PRESTAÇÃO DOS SERVIÇOS DE DISPONIBILIDADE DE ACESSO AO AMBIENTE REMOTO SERVIÇOS TÉCNICOS DE INFORMÁTICA REDE MUNDIAL INTERNET,FORN</t>
+          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.016/2015; PRESTAÇÃO DOS SERVIÇOS EVENTUAIS DE INFORMÁTICA À PGE, NOS MESES DE NOVEMBRO E DEZEMBRO/2014, CONFORME TERMO DE CONTRATO Nº.12/201</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2015NE00094</t>
+          <t>2015NE00095</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9115,19 +9115,19 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.007/2015; PRESTAÇÃO DOS SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE EXECUÇÃO FISCAL ELETRÔNICA, NO DATA CENTER DA PRODAM, NA SEDE DA PGE, NOS MESES</t>
+          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.008/2015; PRESTAÇÃO DOS SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE EXECUÇÃO FISCAL ELETRÔNICA, NO DATA CENTER DA PRODAM, NA SEDE DA PGE, NO MÊS DE</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2015NE00093</t>
+          <t>2015NE00096</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>2499.09</v>
+        <v>40523.13</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.014/2015; PRESTAÇÃO DOS SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP-CADASTRO E FOLHA DE PAGTO.DE PESSOAL DA PGE, NOS MESES DE NOVEMBRO E DEZEM</t>
+          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.009/2015; PRESTAÇÃO DOS SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE EXECUÇÃO FISCAL ELETRÔNICA, NO DATA CENTER DA PRODAM, NA SEDE DA PGE, NO MÊS DE</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9182,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2015NE00096</t>
+          <t>2015NE00093</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>40523.13</v>
+        <v>2499.09</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9205,14 +9205,14 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.009/2015; PRESTAÇÃO DOS SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE EXECUÇÃO FISCAL ELETRÔNICA, NO DATA CENTER DA PRODAM, NA SEDE DA PGE, NO MÊS DE</t>
+          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.014/2015; PRESTAÇÃO DOS SERVIÇOS DE PROCESSAMENTO DO SISTEMA CFPP-CADASTRO E FOLHA DE PAGTO.DE PESSOAL DA PGE, NOS MESES DE NOVEMBRO E DEZEM</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2015NE00095</t>
+          <t>2015NE00094</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.008/2015; PRESTAÇÃO DOS SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE EXECUÇÃO FISCAL ELETRÔNICA, NO DATA CENTER DA PRODAM, NA SEDE DA PGE, NO MÊS DE</t>
+          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.007/2015; PRESTAÇÃO DOS SERVIÇOS DE HOSPEDAGEM DO SISTEMA DE EXECUÇÃO FISCAL ELETRÔNICA, NO DATA CENTER DA PRODAM, NA SEDE DA PGE, NOS MESES</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2015NE00090</t>
+          <t>2015NE00091</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>1801.28</v>
+        <v>8033.08</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9265,28 +9265,24 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.016/2015; PRESTAÇÃO DOS SERVIÇOS EVENTUAIS DE INFORMÁTICA À PGE, NOS MESES DE NOVEMBRO E DEZEMBRO/2014, CONFORME TERMO DE CONTRATO Nº.12/201</t>
+          <t>FOLHA DE INFORMAÇÃO DE DESPESAS DE EXERCÍCIOS ANTERIORES Nº.015/2015; PRESTAÇÃO DOS SERVIÇOS DE DISPONIBILIDADE DE ACESSO AO AMBIENTE REMOTO SERVIÇOS TÉCNICOS DE INFORMÁTICA REDE MUNDIAL INTERNET,FORN</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2025NE0000009</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>6/2019</t>
-        </is>
-      </c>
+          <t>2025NE0000006</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr">
         <is>
           <t>02/01/2025</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>50000</v>
+        <v>372671.34</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -9295,7 +9291,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
@@ -9332,17 +9328,21 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2025NE0000006</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr"/>
+          <t>2025NE0000009</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>6/2019</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
           <t>02/01/2025</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>372671.34</v>
+        <v>50000</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -9351,28 +9351,24 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2024NE0000047</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>11/2021</t>
-        </is>
-      </c>
+          <t>2024NE0000016</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>1006.48</v>
+        <v>345041.98</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -9381,19 +9377,19 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
+          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2024NE0000015</t>
+          <t>2024NE0000037</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9402,7 +9398,7 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>12295.5</v>
+        <v>117343.74</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -9411,19 +9407,19 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
+          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2024NE0000037</t>
+          <t>2024NE0000015</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9432,7 +9428,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>117343.74</v>
+        <v>12295.5</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -9441,24 +9437,28 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Contratação para reajustar em 25%o valor do Contrato, para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,c</t>
+          <t>Contratação para a prestação de Serviços Técnicos especializados em Informática, contemplando os serviços de Execução do Sistema de Recursos Humanos e Folha-PRODAM-RH e Licença de usos do Sistema de I</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2024NE0000016</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr"/>
+          <t>2024NE0000047</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>11/2021</t>
+        </is>
+      </c>
       <c r="C312" t="inlineStr">
         <is>
           <t>02/01/2024</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>345041.98</v>
+        <v>1006.48</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9467,19 +9467,19 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Convênio de Cessão de Servidor nº.002/2023-PGE,cujo objeto é a cessão por disposição da PRODAM-Processamento de Dados Amazonas s/a, de servidores á Procuradoria Geral do Estado d</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE. TC: 0011/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2023NE0000008</t>
+          <t>2023NE0000004</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>232363.84</v>
+        <v>2012.96</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Contratação para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,cont.os Serv.de Rede,comp. o Acesso Gerenci</t>
+          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE.</t>
         </is>
       </c>
     </row>
@@ -9534,12 +9534,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2023NE0000004</t>
+          <t>2023NE0000008</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9548,7 +9548,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>2012.96</v>
+        <v>232363.84</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9557,19 +9557,19 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Contratação para a Aquisição de Cerificados Digitais para a PGE.</t>
+          <t>Contratação para atender a necessidade da demanda dessa Contratante e em conformidade com a DIRAF 401/2022, para a prestação de serv.Tecnicos espec. em Inf.,cont.os Serv.de Rede,comp. o Acesso Gerenci</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2020NE00029</t>
+          <t>2020NE00028</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>6/2019</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>220267.4</v>
+        <v>31526.6</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9587,19 +9587,19 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede, comp.o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),S</t>
+          <t>Contratação para a prestação de serviços Técnicos especializados em Informática,contemplando os Serviços de Execução do Sistema de Protocolo Web-SPROWEB, Execução do Sistema de Recursos Humanos e Folh</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2020NE00028</t>
+          <t>2020NE00029</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>6/2019</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>31526.6</v>
+        <v>220267.4</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -9617,24 +9617,28 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços Técnicos especializados em Informática,contemplando os Serviços de Execução do Sistema de Protocolo Web-SPROWEB, Execução do Sistema de Recursos Humanos e Folh</t>
+          <t>Contratação para a prest.de Serv.Técnicos Especializados em Informática,contemp.os Serviços de Rede, comp.o Acesso Gerenciado à Internet e a Disponibilização de Clientes VPN(Virtual Private Network),S</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2019NE00041</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr"/>
+          <t>2019NE00018</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>5/2018</t>
+        </is>
+      </c>
       <c r="C318" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>2730</v>
+        <v>8065.5</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9643,19 +9647,19 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Referente a Anulação da NE nº.0036,por motivo da Elaboração do novo Termo de Contrato a ser celebrado entre a PGE e a Prodam S.A.</t>
+          <t>Contratação para a prestação de serviços de rede,compreendendo a disponibilização de clientes VPN(Virtual Private Network), para a Procuradoria Geral do Estado.</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2019NE00036</t>
+          <t>2019NE00019</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9664,7 +9668,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>2730</v>
+        <v>120704.01</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -9673,19 +9677,19 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
+          <t>Contratação para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Prodam.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2019NE00020</t>
+          <t>2019NE00016</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>7/2018</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9694,7 +9698,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>748.2</v>
+        <v>12240</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -9703,19 +9707,19 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de licenciamento de uso do INTEGRA perfil intermediário, para a Procuradoria Geral do Estado.</t>
+          <t>Contratação para prestação dos serviços de Acesso Gerenciado à Internet, através da Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2019NE00015</t>
+          <t>2019NE00017</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9724,7 +9728,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>3534.21</v>
+        <v>742.5</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -9733,7 +9737,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de Serviços Eventuais de Informática</t>
+          <t>Contratação para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
         </is>
       </c>
     </row>
@@ -9770,12 +9774,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2019NE00017</t>
+          <t>2019NE00015</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9784,7 +9788,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>742.5</v>
+        <v>3534.21</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -9793,19 +9797,19 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
+          <t>Contratação para a prestação de Serviços Eventuais de Informática</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2019NE00016</t>
+          <t>2019NE00020</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>7/2018</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9814,7 +9818,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>12240</v>
+        <v>748.2</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -9823,19 +9827,19 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Contratação para prestação dos serviços de Acesso Gerenciado à Internet, através da Rede de Governo.</t>
+          <t>Contratação para a prestação dos serviços de licenciamento de uso do INTEGRA perfil intermediário, para a Procuradoria Geral do Estado.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2019NE00019</t>
+          <t>2019NE00036</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9844,7 +9848,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>120704.01</v>
+        <v>2730</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -9853,28 +9857,24 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Prodam.</t>
+          <t>Contratação para a prestação de serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2019NE00018</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>5/2018</t>
-        </is>
-      </c>
+          <t>2019NE00041</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
           <t>02/01/2019</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>8065.5</v>
+        <v>2730</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -9883,19 +9883,19 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de rede,compreendendo a disponibilização de clientes VPN(Virtual Private Network), para a Procuradoria Geral do Estado.</t>
+          <t>Referente a Anulação da NE nº.0036,por motivo da Elaboração do novo Termo de Contrato a ser celebrado entre a PGE e a Prodam S.A.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2018NE00067</t>
+          <t>2018NE00066</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>14568.18</v>
+        <v>7068.42</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -9913,19 +9913,19 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Execução de Sistemas Prodam-RH.</t>
+          <t>Contratação para a prestação de serviços Eventuais de Informática</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2018NE00069</t>
+          <t>2018NE00068</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>24480</v>
+        <v>225741.6</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -9943,19 +9943,19 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
+          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2018NE00065</t>
+          <t>2018NE00070</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>746.48</v>
+        <v>28472.88</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -9973,19 +9973,19 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com serviços de backup e segurança.</t>
+          <t>Contratação para a prestação dos serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2018NE00070</t>
+          <t>2018NE00065</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9994,7 +9994,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>28472.88</v>
+        <v>746.48</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10003,19 +10003,19 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
+          <t>Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com serviços de backup e segurança.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2018NE00068</t>
+          <t>2018NE00069</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>225741.6</v>
+        <v>24480</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10033,19 +10033,19 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
+          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2018NE00066</t>
+          <t>2018NE00067</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>7068.42</v>
+        <v>14568.18</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -10063,19 +10063,19 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços Eventuais de Informática</t>
+          <t>Contratação para os serviços de Execução de Sistemas Prodam-RH.</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2017NE00021</t>
+          <t>2017NE00036</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>16320</v>
+        <v>2239.44</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -10093,19 +10093,19 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Contrato nº.008/2016-PGE.</t>
+          <t>Referente ao 3º. Termo Aditivo ao Contrato nº.02/2015-PGE.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2017NE00022</t>
+          <t>2017NE00025</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10114,7 +10114,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>27746.12</v>
+        <v>5990.4</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -10123,19 +10123,19 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Referente ao Termo de Contrato nº.09/2016-PGE.</t>
+          <t>Referente ao 3º. Termo Aditivo ao Contrato nº.012/2014-PGE.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2017NE00024</t>
+          <t>2017NE00020</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10144,7 +10144,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>686.17</v>
+        <v>153058.28</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Referente ao 2º. Termo Aditivo ao Contrato nº.02/2015-PGE.</t>
+          <t>Referente ao 4º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2017NE00020</t>
+          <t>2017NE00024</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>153058.28</v>
+        <v>686.17</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -10213,19 +10213,19 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Referente ao 4º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
+          <t>Referente ao 2º. Termo Aditivo ao Contrato nº.02/2015-PGE.</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2017NE00025</t>
+          <t>2017NE00022</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>5990.4</v>
+        <v>27746.12</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -10243,19 +10243,19 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Referente ao 3º. Termo Aditivo ao Contrato nº.012/2014-PGE.</t>
+          <t>Referente ao Termo de Contrato nº.09/2016-PGE.</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2017NE00036</t>
+          <t>2017NE00021</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>2239.44</v>
+        <v>16320</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10273,19 +10273,19 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Referente ao 3º. Termo Aditivo ao Contrato nº.02/2015-PGE.</t>
+          <t>Referente ao Termo de Contrato nº.008/2016-PGE.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2014NE00011</t>
+          <t>2014NE00007</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>3/2009</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>6337.9</v>
+        <v>23312.69</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -10303,19 +10303,19 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Contrato No. 5/2010 - CFPP - Cadastro Folha de Pagto de Pessoal</t>
+          <t>Contrato No. 3/2009 - Serviços Eventuais de Informatica</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2014NE00009</t>
+          <t>2014NE00029</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>17738.15</v>
+        <v>149980.18</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10333,19 +10333,19 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Contrato No. 4/2011 - Acesso … Internet 1,5 Mbps</t>
+          <t>Contrato No. 1/2012 - Hospedagem do Sistema Execução Fiscal Eletrônica</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2014NE00029</t>
+          <t>2014NE00009</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>149980.18</v>
+        <v>17738.15</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10363,19 +10363,19 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Contrato No. 1/2012 - Hospedagem do Sistema Execução Fiscal Eletrônica</t>
+          <t>Contrato No. 4/2011 - Acesso … Internet 1,5 Mbps</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2014NE00007</t>
+          <t>2014NE00011</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>3/2009</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>23312.69</v>
+        <v>6337.9</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10393,19 +10393,19 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Contrato No. 3/2009 - Serviços Eventuais de Informatica</t>
+          <t>Contrato No. 5/2010 - CFPP - Cadastro Folha de Pagto de Pessoal</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2017NE00348</t>
+          <t>2017NE00349</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>2428.03</v>
+        <v>37623.6</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -10423,19 +10423,19 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Execução de Sistemas Prodam-RH.</t>
+          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2017NE00357</t>
+          <t>2017NE00347</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10444,7 +10444,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1178.07</v>
+        <v>4080</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10453,19 +10453,19 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços Eventuais de Informática</t>
+          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2017NE00351</t>
+          <t>2017NE00345</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10474,7 +10474,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>2389.25</v>
+        <v>746.48</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
+          <t>Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com serviços de backup e segurança.</t>
         </is>
       </c>
     </row>
@@ -10520,12 +10520,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2017NE00345</t>
+          <t>2017NE00351</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>746.48</v>
+        <v>2389.25</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -10543,19 +10543,19 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com serviços de backup e segurança.</t>
+          <t>Contratação para a prestação dos serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2017NE00347</t>
+          <t>2017NE00357</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>4080</v>
+        <v>1178.07</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10573,19 +10573,19 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
+          <t>Contratação para a prestação de serviços Eventuais de Informática</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2017NE00349</t>
+          <t>2017NE00348</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>37623.6</v>
+        <v>2428.03</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -10603,14 +10603,14 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
+          <t>Contratação para os serviços de Execução de Sistemas Prodam-RH.</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2016NE00354</t>
+          <t>2016NE00348</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -10620,7 +10620,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.02</v>
+        <v>4080</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10629,14 +10629,14 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total da NE nº.028,relativa ao 4º.Termo Aditivo ao Contrato nº.04/2011-PGE,por valores não liquidados, no período de vigência do Termo.</t>
+          <t>Referente ao reforço da NE nº.0313.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2016NE00343</t>
+          <t>2016NE00347</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>38264.57</v>
+        <v>1497.6</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -10655,14 +10655,14 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Reforço da NE nº.00252</t>
+          <t>Referente ao reforço da NE nº.00271.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2016NE00350</t>
+          <t>2016NE00352</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>2428.03</v>
+        <v>11560.1</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0314.</t>
+          <t>Referente a Anulação parcial da NE nº00027,referente ao Termo de Contrato nº.006/2015,por valores não liquidados no período de vigência do Termo de Contrato.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2016NE00352</t>
+          <t>2016NE00350</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>11560.1</v>
+        <v>2428.03</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -10733,14 +10733,14 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Referente a Anulação parcial da NE nº00027,referente ao Termo de Contrato nº.006/2015,por valores não liquidados no período de vigência do Termo de Contrato.</t>
+          <t>Referente ao reforço da NE nº.0314.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2016NE00347</t>
+          <t>2016NE00343</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1497.6</v>
+        <v>38264.57</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -10759,14 +10759,14 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.00271.</t>
+          <t>Reforço da NE nº.00252</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2016NE00348</t>
+          <t>2016NE00354</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -10776,7 +10776,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>4080</v>
+        <v>0.02</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -10785,14 +10785,14 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Referente ao reforço da NE nº.0313.</t>
+          <t>Referente a Anulação Total da NE nº.028,relativa ao 4º.Termo Aditivo ao Contrato nº.04/2011-PGE,por valores não liquidados, no período de vigência do Termo.</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2015NE00392</t>
+          <t>2015NE00398</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -10802,7 +10802,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>6328.57</v>
+        <v>2764.17</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2015NE00405</t>
+          <t>2015NE00393</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>29722.38</v>
+        <v>2493.12</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2015NE00391</t>
+          <t>2015NE00363</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -10854,7 +10854,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>661.0700000000001</v>
+        <v>104482.14</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2015NE00363</t>
+          <t>2015NE00391</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>104482.14</v>
+        <v>661.0700000000001</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2015NE00393</t>
+          <t>2015NE00405</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>2493.12</v>
+        <v>29722.38</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2015NE00398</t>
+          <t>2015NE00392</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -10958,7 +10958,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>2764.17</v>
+        <v>6328.57</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -10974,21 +10974,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2019NE00327</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>2/2015</t>
-        </is>
-      </c>
+          <t>2019NE00326</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr">
         <is>
           <t>01/11/2019</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>805.5</v>
+        <v>10</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -10997,28 +10993,24 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0047,relativo ao 5º. Termo Aditivo ao Contrato nº002/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A,para a prestação de serviços de Hosped</t>
+          <t>Referente ao Reforço da NE nº.046, relativo ao Termo de Contrato nº.002/2019-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2019NE00329</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>7/2018</t>
-        </is>
-      </c>
+          <t>2019NE00323</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
       <c r="C366" t="inlineStr">
         <is>
           <t>01/11/2019</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>261.06</v>
+        <v>10910</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11027,24 +11019,28 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE Nº.0229 relativo ao 1º. Termo Aditivo ao Contº.nº.007/2018-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
+          <t>Referente a Anulação Parcial do saldo da NE Nº.014, relativo ao 3º.Termo Aditivo ao Contº.nº.06/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para os serviços de Exec</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2019NE00323</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr"/>
+          <t>2019NE00329</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>7/2018</t>
+        </is>
+      </c>
       <c r="C367" t="inlineStr">
         <is>
           <t>01/11/2019</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>10910</v>
+        <v>261.06</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11053,24 +11049,28 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Referente a Anulação Parcial do saldo da NE Nº.014, relativo ao 3º.Termo Aditivo ao Contº.nº.06/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A, para os serviços de Exec</t>
+          <t>Referente ao Reforço da NE Nº.0229 relativo ao 1º. Termo Aditivo ao Contº.nº.007/2018-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2019NE00326</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr"/>
+          <t>2019NE00327</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2/2015</t>
+        </is>
+      </c>
       <c r="C368" t="inlineStr">
         <is>
           <t>01/11/2019</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>10</v>
+        <v>805.5</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11079,19 +11079,19 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.046, relativo ao Termo de Contrato nº.002/2019-PGE,celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A</t>
+          <t>Referente ao Reforço da NE nº.0047,relativo ao 5º. Termo Aditivo ao Contrato nº002/2015-PGE, celebrado entre a PGE e a Prodam Processamento de Dados Amazonas S/A,para a prestação de serviços de Hosped</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2017NE00296</t>
+          <t>2017NE00297</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>6936.53</v>
+        <v>2312</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11109,19 +11109,19 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Contratação para a Execução de Sistema de Protocolo em Plataforma Web(Sproweb), para a PGE.</t>
+          <t>Contratação para os serviços de Acesso Gerenciado à Internet, através da Rede de Governo</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2017NE00292</t>
+          <t>2017NE00294</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1472.59</v>
+        <v>1375.89</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -11139,19 +11139,19 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços Eventuais de Informática, para o prédio da PGE.</t>
+          <t>Contratação para os serviços de Execução de Sistemas PRODAM-RH.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2017NE00299</t>
+          <t>2017NE00295</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>746.48</v>
+        <v>37623.6</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com serviços de backup e segurança.</t>
+          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
         </is>
       </c>
     </row>
@@ -11206,12 +11206,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2017NE00295</t>
+          <t>2017NE00299</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>37623.6</v>
+        <v>746.48</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11229,19 +11229,19 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de disponibilidade de 4 máquinas virtuais e infraestrutura de comunicação e armazenamento de dados, para Hospedar o Sistema de Execução Fiscal Eletrônica, no Data Center d</t>
+          <t>Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com serviços de backup e segurança.</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2017NE00294</t>
+          <t>2017NE00292</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11250,7 +11250,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1375.89</v>
+        <v>1472.59</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -11259,19 +11259,19 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Execução de Sistemas PRODAM-RH.</t>
+          <t>Contratação para a prestação dos serviços Eventuais de Informática, para o prédio da PGE.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2017NE00297</t>
+          <t>2017NE00296</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11280,7 +11280,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>2312</v>
+        <v>6936.53</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Acesso Gerenciado à Internet, através da Rede de Governo</t>
+          <t>Contratação para a Execução de Sistema de Protocolo em Plataforma Web(Sproweb), para a PGE.</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2015NE00315</t>
+          <t>2015NE00314</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11336,7 +11336,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>29722.38</v>
+        <v>300</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -11345,19 +11345,19 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Anulação total da NE 191/2015 para correção do nº do Processo referente ao 4º Termo Aditivo ao Contrato nº 004/2011-PGE.</t>
+          <t>Prestação de serviços ref. ao 4º termo Aditivo ao cont 04/2011-PGE.</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2015NE00313</t>
+          <t>2015NE00316</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>356.08</v>
+        <v>29722.38</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11375,19 +11375,19 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Anulação total da NE 06/2015 por saldo de valores não liquidados.</t>
+          <t>Referente a prestação de serviços de disponibilidade de acesso remoto, conforme 4º Termo Aditivo ao Contrato 04/2011-PGE.</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2015NE00316</t>
+          <t>2015NE00313</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11396,7 +11396,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>29722.38</v>
+        <v>356.08</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11405,14 +11405,14 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Referente a prestação de serviços de disponibilidade de acesso remoto, conforme 4º Termo Aditivo ao Contrato 04/2011-PGE.</t>
+          <t>Anulação total da NE 06/2015 por saldo de valores não liquidados.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2015NE00314</t>
+          <t>2015NE00315</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11426,7 +11426,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>300</v>
+        <v>29722.38</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -11435,14 +11435,14 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Prestação de serviços ref. ao 4º termo Aditivo ao cont 04/2011-PGE.</t>
+          <t>Anulação total da NE 191/2015 para correção do nº do Processo referente ao 4º Termo Aditivo ao Contrato nº 004/2011-PGE.</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2018NE00339</t>
+          <t>2018NE00338</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -11452,7 +11452,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>7672.78</v>
+        <v>1703.32</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.070,no valor de R$7.672,78,para atender a Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07.02.2018,referente ao 1º.Termo Aditivo ao Contrato nº.009/2016-PGE,</t>
+          <t>Referente a Anulação Total do saldo da NE nº.067,no valor de R$1.703,32,para atender a Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07.02.2018,referente ao 2º.Termo Aditivo ao Contrato nº.006/2015-PGE,</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2018NE00338</t>
+          <t>2018NE00339</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -11504,7 +11504,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>1703.32</v>
+        <v>7672.78</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.067,no valor de R$1.703,32,para atender a Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07.02.2018,referente ao 2º.Termo Aditivo ao Contrato nº.006/2015-PGE,</t>
+          <t>Referente a Anulação Total do saldo da NE nº.070,no valor de R$7.672,78,para atender a Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07.02.2018,referente ao 1º.Termo Aditivo ao Contrato nº.009/2016-PGE,</t>
         </is>
       </c>
     </row>
@@ -11550,21 +11550,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2016NE00271</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>12/2014</t>
-        </is>
-      </c>
+          <t>2016NE00270</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
       <c r="C385" t="inlineStr">
         <is>
           <t>01/09/2016</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>399.38</v>
+        <v>400</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11573,24 +11569,28 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Objeto:Reajustar o valor do Termo de Contrato nº.012/2014-PGE em 11,09%, com base no IGPM do período e prorrogar o prazo de vigência por 12 meses, da prestação dos serviços Eventuais de Informática pa</t>
+          <t>Referente a Anulação Parcial da NE nº.0031, por saldo não liquidado nos meses de Janeiro a Julho/2016.</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2016NE00270</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr"/>
+          <t>2016NE00271</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>12/2014</t>
+        </is>
+      </c>
       <c r="C386" t="inlineStr">
         <is>
           <t>01/09/2016</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>400</v>
+        <v>399.38</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Referente a Anulação Parcial da NE nº.0031, por saldo não liquidado nos meses de Janeiro a Julho/2016.</t>
+          <t>Objeto:Reajustar o valor do Termo de Contrato nº.012/2014-PGE em 11,09%, com base no IGPM do período e prorrogar o prazo de vigência por 12 meses, da prestação dos serviços Eventuais de Informática pa</t>
         </is>
       </c>
     </row>
@@ -11658,12 +11658,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2017NE00204</t>
+          <t>2017NE00202</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>8160</v>
+        <v>4856.06</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -11681,19 +11681,19 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0021, relativa ao Termo de Contrato nº.008/2016-PGE. Contratação para os serviços de Acesso Gerenciado à Internet, através da Rede de Governo</t>
+          <t>Referente ao Reforço da NE nº.0023, relativa ao 1º. Termo Aditivo ao Contrato nº.006/2015-PGE. Contratação para os serviços de Execução de Sistemas PRODAM-RH.</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2017NE00201</t>
+          <t>2017NE00203</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>1492.96</v>
+        <v>1098.24</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11711,19 +11711,19 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0036, relativa ao 3º. Termo Aditivo ao Contrato nº.02/2015-PGE. Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com ser</t>
+          <t>Referente ao Reforço da NE nº.0025,relativa ao 3º. Termo Aditivo ao Contrato nº.012/2014-PGE. Contratação para os serviços de Informática de Forma Eventual, mediante a utilização de pessoal e equipame</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2017NE00203</t>
+          <t>2017NE00201</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>1098.24</v>
+        <v>1492.96</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -11741,19 +11741,19 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0025,relativa ao 3º. Termo Aditivo ao Contrato nº.012/2014-PGE. Contratação para os serviços de Informática de Forma Eventual, mediante a utilização de pessoal e equipame</t>
+          <t>Referente ao Reforço da NE nº.0036, relativa ao 3º. Termo Aditivo ao Contrato nº.02/2015-PGE. Contratação para os serviços de Hospedagem do Site da PGE, na infraestrutura tecnológica da Prodam,com ser</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2017NE00202</t>
+          <t>2017NE00204</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11762,7 +11762,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>4856.06</v>
+        <v>8160</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Referente ao Reforço da NE nº.0023, relativa ao 1º. Termo Aditivo ao Contrato nº.006/2015-PGE. Contratação para os serviços de Execução de Sistemas PRODAM-RH.</t>
+          <t>Referente ao Reforço da NE nº.0021, relativa ao Termo de Contrato nº.008/2016-PGE. Contratação para os serviços de Acesso Gerenciado à Internet, através da Rede de Governo</t>
         </is>
       </c>
     </row>
@@ -11808,12 +11808,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2016NE00195</t>
+          <t>2016NE00196</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>3774.66</v>
+        <v>2058.51</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -11831,19 +11831,19 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objeto:Contratação para prorrogar a vigência por 12(doze) meses, da prestação dos Serviços Técnicos em Informática de Forma Eventual, para a PGE; Fundamentação Legal:Parecer nº.1107/2014-ASS/CGL, Ata </t>
+          <t>Objeto:Prorrogação do prazo de vigência do contrato original por mais 12(doze) meses a contar da data de sua assinatura,conforme cláusula oitava do contrato e reajustar,com base no IGPM,em 10,09% do v</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2016NE00196</t>
+          <t>2016NE00195</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11852,7 +11852,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>2058.51</v>
+        <v>3774.66</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Objeto:Prorrogação do prazo de vigência do contrato original por mais 12(doze) meses a contar da data de sua assinatura,conforme cláusula oitava do contrato e reajustar,com base no IGPM,em 10,09% do v</t>
+          <t xml:space="preserve">Objeto:Contratação para prorrogar a vigência por 12(doze) meses, da prestação dos Serviços Técnicos em Informática de Forma Eventual, para a PGE; Fundamentação Legal:Parecer nº.1107/2014-ASS/CGL, Ata </t>
         </is>
       </c>
     </row>
@@ -11898,12 +11898,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2015NE00123</t>
+          <t>2015NE00137</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>1/2012</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11912,7 +11912,7 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>7864</v>
+        <v>25017.55</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -11921,19 +11921,19 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Supressão de 48,15% no valor do Contrato 012/2014 1º Termo Aditivo - Serviços Eventuais</t>
+          <t>Folha de Informação de Despesas de Exercícios Anteriores nº.006/2015; Referente ao pagamento pela prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Proda</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2015NE00161</t>
+          <t>2015NE00159</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -11942,7 +11942,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>6560.33</v>
+        <v>34444.66</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -11951,19 +11951,19 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Cobertura Financeira abril e maio 2015</t>
+          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2015NE00125</t>
+          <t>2015NE00122</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>5609.52</v>
+        <v>1899.96</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -11981,19 +11981,19 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Referente ao 1º Termo Aditivo ao Contrato 002/2015 - Hospedagem de Site</t>
+          <t>Referente a supressão de 20% no valor do contrato 005/2010 - 5º Termo Aditivo - CFPP</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2015NE00122</t>
+          <t>2015NE00125</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12002,7 +12002,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>1899.96</v>
+        <v>5609.52</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -12011,19 +12011,19 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Referente a supressão de 20% no valor do contrato 005/2010 - 5º Termo Aditivo - CFPP</t>
+          <t>Referente ao 1º Termo Aditivo ao Contrato 002/2015 - Hospedagem de Site</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2015NE00159</t>
+          <t>2015NE00161</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>34444.66</v>
+        <v>6560.33</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12041,19 +12041,19 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 18/09/2015</t>
+          <t>Cobertura Financeira abril e maio 2015</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2015NE00137</t>
+          <t>2015NE00123</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>1/2012</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>25017.55</v>
+        <v>7864</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12071,19 +12071,19 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Folha de Informação de Despesas de Exercícios Anteriores nº.006/2015; Referente ao pagamento pela prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Proda</t>
+          <t>Supressão de 48,15% no valor do Contrato 012/2014 1º Termo Aditivo - Serviços Eventuais</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2019NE00076</t>
+          <t>2019NE00075</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>12/2014</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12092,7 +12092,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>742.26</v>
+        <v>1209.84</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12101,19 +12101,19 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Ref. ao pagto. de Despesa de Exercícios Anteriores,pela prestação de Serviços de Hospedagem do Site da PGE, no mês de Outubro/2018, conf. NFS-e nº.4503 emitida em 15.10.2018 e 4º.Termo Aditivo ao Cont</t>
+          <t>Ref.ao pagto. de Desp.de Exerc.Anteriores,pela prest.de Serviços Eventuais de Informática para a PGE, no mês de Dezembro/2018, conf.NFS-e nº.5559/2018, emit. em 06.12.2018 e 6º. T.Adit.ao Contº. nº.01</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2019NE00075</t>
+          <t>2019NE00076</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>12/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1209.84</v>
+        <v>742.26</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -12131,24 +12131,28 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Ref.ao pagto. de Desp.de Exerc.Anteriores,pela prest.de Serviços Eventuais de Informática para a PGE, no mês de Dezembro/2018, conf.NFS-e nº.5559/2018, emit. em 06.12.2018 e 6º. T.Adit.ao Contº. nº.01</t>
+          <t>Ref. ao pagto. de Despesa de Exercícios Anteriores,pela prestação de Serviços de Hospedagem do Site da PGE, no mês de Outubro/2018, conf. NFS-e nº.4503 emitida em 15.10.2018 e 4º.Termo Aditivo ao Cont</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2018NE00160</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr"/>
+          <t>2018NE00183</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>12/2014</t>
+        </is>
+      </c>
       <c r="C405" t="inlineStr">
         <is>
           <t>01/03/2018</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>18981.92</v>
+        <v>4712.28</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -12157,14 +12161,14 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.0070, no valor de R$18.981,92,para acerto na natureza de despesa, conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 1º.Termo Ad</t>
+          <t>Contratação para a prestação dos serviços Eventuais de Informática, para a PGE.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2018NE00156</t>
+          <t>2018NE00164</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -12174,7 +12178,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>4712.28</v>
+        <v>0.22</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12183,19 +12187,19 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referente a Anulação Total do saldo da NE nº.0066, no valor de R$4.712,28, para acerto na natureza de despesa, Conforme Orientação Técnica nº.12/2018-GINS/SEFAZ, de 07/02/2018; Referente ao 5º. Termo </t>
+          <t>Referente a Anulação Total do saldo da NE nº.065, no valor de R$0,22, para acerto na natureza de despesa, conforme Orientação Técnica nº.12//2018-GINS/SEFAZ, de 07/02/2018; Referente ao 3º.Termo Aditi</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2018NE00186</t>
+          <t>2018NE00187</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>8/2016</t>
+          <t>9/2016</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12204,7 +12208,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>16320</v>
+        <v>18981.92</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12213,21 +12217,17 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
+          <t>Contratação para a prestação dos serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2018NE00188</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>2/2015</t>
-        </is>
-      </c>
+          <t>2018NE00162</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
       <c r="C408" t="inlineStr">
         <is>
           <t>01/03/2018</t>
@@ -12243,19 +12243,19 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
+          <t>Referente a Anulação Total do saldo da NE nº.0077, no valor de R$3.712,50 para acerto na natureza de despesa, conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 4º.Termo Adi</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2018NE00185</t>
+          <t>2018NE00184</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>6/2015</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12264,7 +12264,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>150494.4</v>
+        <v>9712.120000000001</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12273,14 +12273,14 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Prodam.</t>
+          <t>Contratação para os serviços de Execução de Sistemas Prodam-RH</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2018NE00159</t>
+          <t>2018NE00157</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -12290,7 +12290,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>16320</v>
+        <v>9712.120000000001</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.0069, no valor de R$16.320,00 para acerto na natureza de despesa, conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 1º.Termo Ad</t>
+          <t>Referente a Anulação Total do saldo da NE nº.0067, no valor de R$9.712,12, para acerto na natureza de despesa, Conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 2º. Termo A</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2018NE00157</t>
+          <t>2018NE00159</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>9712.120000000001</v>
+        <v>16320</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12351,19 +12351,19 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.0067, no valor de R$9.712,12, para acerto na natureza de despesa, Conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 2º. Termo A</t>
+          <t>Referente a Anulação Total do saldo da NE nº.0069, no valor de R$16.320,00 para acerto na natureza de despesa, conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 1º.Termo Ad</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2018NE00184</t>
+          <t>2018NE00185</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>6/2015</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>9712.120000000001</v>
+        <v>150494.4</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -12381,17 +12381,21 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>Contratação para os serviços de Execução de Sistemas Prodam-RH</t>
+          <t>Contratação para a prestação dos serviços de Hospedagem do Sistema de Execução Fiscal Eletrônica, no Data Center da Prodam.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2018NE00162</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr"/>
+          <t>2018NE00188</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2/2015</t>
+        </is>
+      </c>
       <c r="C414" t="inlineStr">
         <is>
           <t>01/03/2018</t>
@@ -12407,19 +12411,19 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.0077, no valor de R$3.712,50 para acerto na natureza de despesa, conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 4º.Termo Adi</t>
+          <t>Contratação para a prestação de serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2018NE00187</t>
+          <t>2018NE00186</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>9/2016</t>
+          <t>8/2016</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12428,7 +12432,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>18981.92</v>
+        <v>16320</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -12437,14 +12441,14 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
+          <t>Contratação para a prestação dos serviços de Acesso Gerenciado à Internet,através da Rede de Governo.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2018NE00164</t>
+          <t>2018NE00156</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -12454,7 +12458,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>0.22</v>
+        <v>4712.28</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -12463,28 +12467,24 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Referente a Anulação Total do saldo da NE nº.065, no valor de R$0,22, para acerto na natureza de despesa, conforme Orientação Técnica nº.12//2018-GINS/SEFAZ, de 07/02/2018; Referente ao 3º.Termo Aditi</t>
+          <t xml:space="preserve">Referente a Anulação Total do saldo da NE nº.0066, no valor de R$4.712,28, para acerto na natureza de despesa, Conforme Orientação Técnica nº.12/2018-GINS/SEFAZ, de 07/02/2018; Referente ao 5º. Termo </t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2018NE00183</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>12/2014</t>
-        </is>
-      </c>
+          <t>2018NE00160</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
       <c r="C417" t="inlineStr">
         <is>
           <t>01/03/2018</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>4712.28</v>
+        <v>18981.92</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -12493,14 +12493,14 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços Eventuais de Informática, para a PGE.</t>
+          <t>Referente a Anulação Total do saldo da NE nº.0070, no valor de R$18.981,92,para acerto na natureza de despesa, conforme Orientação Técnica nº.12/2018-GINS/SEFAZ,de 07/02/2018; Referente ao 1º.Termo Ad</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2016NE00067</t>
+          <t>2016NE00065</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -12514,7 +12514,7 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>1606.6</v>
+        <v>4016.54</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -12523,19 +12523,19 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE,mantém com a Prodam,no per.d</t>
+          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2016NE00069</t>
+          <t>2016NE00083</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -12544,7 +12544,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>4016.54</v>
+        <v>721.96</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -12553,19 +12553,19 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE mantém com a Prodam,no mês d</t>
+          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Processamento do Sistema CFPP-Cadastro e Folha de Pagto.de Pessoal da PGE, no período de 01 a 19/11/2015, conforme 6º. Termo Aditivo ao</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2016NE00068</t>
+          <t>2016NE00082</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>4016.54</v>
+        <v>886.5</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -12583,19 +12583,19 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE mantém com a Prodam,no mês d</t>
+          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Processamento do Sistema CFPP-Cadastro e Folha de Pagto.de Pessoal da PGE, no mês de Outubro/2015, conforme 6º. Termo Aditivo ao Contra</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2016NE00063</t>
+          <t>2016NE00081</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>4016.54</v>
+        <v>623.27</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -12613,19 +12613,19 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
+          <t>Ref.ao pagto.de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site,na infraestrutura da Prodam,no mês de Agôsto/2015,co</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2016NE00070</t>
+          <t>2016NE00080</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>4016.54</v>
+        <v>623.28</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -12643,19 +12643,19 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE mantém com a Prodam,no mês d</t>
+          <t>Ref.ao pagto. de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site,na infraestrutura da Prodam,no mês de Dez/2015,conf</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2016NE00066</t>
+          <t>2016NE00084</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>5/2010</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>4016.54</v>
+        <v>877.37</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -12673,19 +12673,19 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
+          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Processamento do Sistema CFPP-Cadastro e Folha de Pagto.de Pessoal da PGE, no mês de Setembro/2015, conforme 6º. Termo Aditivo ao Contr</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2016NE00075</t>
+          <t>2016NE00078</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>34444.66</v>
+        <v>623.28</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -12703,19 +12703,19 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Hospedagem do Sistema PGE.net,no Data Center da Prodam,no mês de Outubro/2015,conforme 3º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
+          <t>Ref.ao pagto.de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site na infraestrutura da Prodam,no mês de Outub/2015,con</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2016NE00076</t>
+          <t>2016NE00079</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -12724,7 +12724,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>34444.66</v>
+        <v>623.28</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -12733,19 +12733,19 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Hospedagem do Sistema PGE.net,no Data Center da Prodam,no mês de Novembro/2015,conforme 3º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
+          <t>Ref.ao pagto. de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site,na infraestrutura da Prodam,no mês de Nov/2015,conf</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2016NE00064</t>
+          <t>2016NE00077</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>4/2011</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -12754,7 +12754,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>4016.54</v>
+        <v>34444.66</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -12763,19 +12763,19 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
+          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Hospedagem do Sistema PGE.net,no Data Center da Prodam,no mês de Dezembro/2015,conforme 3º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2016NE00077</t>
+          <t>2016NE00064</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>7/2014</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12784,7 +12784,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>34444.66</v>
+        <v>4016.54</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -12793,19 +12793,19 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Hospedagem do Sistema PGE.net,no Data Center da Prodam,no mês de Dezembro/2015,conforme 3º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
+          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2016NE00079</t>
+          <t>2016NE00076</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12814,7 +12814,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>623.28</v>
+        <v>34444.66</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -12823,19 +12823,19 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Ref.ao pagto. de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site,na infraestrutura da Prodam,no mês de Nov/2015,conf</t>
+          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Hospedagem do Sistema PGE.net,no Data Center da Prodam,no mês de Novembro/2015,conforme 3º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2016NE00078</t>
+          <t>2016NE00075</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>7/2014</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -12844,7 +12844,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>623.28</v>
+        <v>34444.66</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -12853,19 +12853,19 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site na infraestrutura da Prodam,no mês de Outub/2015,con</t>
+          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Hospedagem do Sistema PGE.net,no Data Center da Prodam,no mês de Outubro/2015,conforme 3º. Termo Aditivo ao Contrato nº.07/2014-PGE.</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2016NE00084</t>
+          <t>2016NE00066</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -12874,7 +12874,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>877.37</v>
+        <v>4016.54</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -12883,19 +12883,19 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Processamento do Sistema CFPP-Cadastro e Folha de Pagto.de Pessoal da PGE, no mês de Setembro/2015, conforme 6º. Termo Aditivo ao Contr</t>
+          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2016NE00080</t>
+          <t>2016NE00070</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12904,7 +12904,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>623.28</v>
+        <v>4016.54</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -12913,19 +12913,19 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Ref.ao pagto. de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site,na infraestrutura da Prodam,no mês de Dez/2015,conf</t>
+          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE mantém com a Prodam,no mês d</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2016NE00081</t>
+          <t>2016NE00063</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12934,7 +12934,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>623.27</v>
+        <v>4016.54</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -12943,19 +12943,19 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.dos serv.de Hospedagem do Site da PGE,contemplando a disponib.dos recursos necessários para a Hospedagem do Site,na infraestrutura da Prodam,no mês de Agôsto/2015,co</t>
+          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2016NE00082</t>
+          <t>2016NE00068</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>886.5</v>
+        <v>4016.54</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -12973,19 +12973,19 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Processamento do Sistema CFPP-Cadastro e Folha de Pagto.de Pessoal da PGE, no mês de Outubro/2015, conforme 6º. Termo Aditivo ao Contra</t>
+          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE mantém com a Prodam,no mês d</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2016NE00083</t>
+          <t>2016NE00069</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>5/2010</t>
+          <t>4/2011</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>721.96</v>
+        <v>4016.54</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -13003,14 +13003,14 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Referente ao pagamento de despesa,pela prestação dos serviços de Processamento do Sistema CFPP-Cadastro e Folha de Pagto.de Pessoal da PGE, no período de 01 a 19/11/2015, conforme 6º. Termo Aditivo ao</t>
+          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE mantém com a Prodam,no mês d</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2016NE00065</t>
+          <t>2016NE00067</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>4016.54</v>
+        <v>1606.6</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -13033,19 +13033,19 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Ref.ao pagto.de despesa,pela prest.de serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunicação a partir do link ótico ponto-a-ponto que a PGE mantém com a Prodam,no mê</t>
+          <t>Ref.ao pagto.de despesa,pela prest.dos serv.Técnicos de Telecomunicações por Rede Mundial Internet em 1,5 MBps,estab.comunic.a partir do link ótico ponto-a-ponto,que a PGE,mantém com a Prodam,no per.d</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2019NE00047</t>
+          <t>2019NE00046</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2/2015</t>
+          <t>2/2019</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -13054,7 +13054,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1611</v>
+        <v>3955.52</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -13063,19 +13063,19 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Contratação para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
+          <t>Contratação para a prestação de serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2019NE00046</t>
+          <t>2019NE00047</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2/2019</t>
+          <t>2/2015</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>3955.52</v>
+        <v>1611</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Contratação para a prestação de serviços de Execução de Sistema de Protocolo em Plataforma Web(Sproweb).</t>
+          <t>Contratação para a prestação dos serviços de Hospedagem do Site na Infraestrutura Tecnológica da Prodam, com serviços de Backup e Segurança.</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/PGE/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/PGE/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2028-01-31</t>
         </is>
       </c>
     </row>
